--- a/data/trans_orig/P64E-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P64E-Estudios-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según el número de personas que trabajan bajo su responsabilidad en 2007</t>
+          <t>Población según el número de personas que trabajan bajo su responsabilidad en 2007 (tasa de respuesta: 98,58%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1017</t>
+          <t>1005</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>8248</t>
+          <t>8264</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -773,7 +773,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>5036</t>
+          <t>4848</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>3,35%</t>
+          <t>3,23%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1028</t>
+          <t>1036</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>10188</t>
+          <t>9225</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -823,7 +823,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,94%</t>
+          <t>1,76%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>817</t>
+          <t>816</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>7908</t>
+          <t>7513</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -866,7 +866,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>2,12%</t>
+          <t>2,01%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>1988</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>821</t>
+          <t>824</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>8793</t>
+          <t>8439</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -936,7 +936,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>1,68%</t>
+          <t>1,61%</t>
         </is>
       </c>
     </row>
@@ -959,12 +959,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>1956</t>
+          <t>1923</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>11754</t>
+          <t>10765</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -974,12 +974,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>0,51%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>3,15%</t>
+          <t>2,88%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -994,12 +994,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>1988</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1009,12 +1009,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1029,12 +1029,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>1964</t>
+          <t>1915</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>11167</t>
+          <t>10941</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1049,7 +1049,7 @@
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>2,13%</t>
+          <t>2,09%</t>
         </is>
       </c>
     </row>
@@ -1072,12 +1072,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>35591</t>
+          <t>35221</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>62588</t>
+          <t>61270</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1087,12 +1087,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>9,53%</t>
+          <t>9,43%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>16,76%</t>
+          <t>16,4%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>926</t>
+          <t>905</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>8149</t>
+          <t>7909</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1122,12 +1122,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>5,42%</t>
+          <t>5,26%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1142,12 +1142,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>35958</t>
+          <t>38365</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>64682</t>
+          <t>66445</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>6,86%</t>
+          <t>7,32%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>12,35%</t>
+          <t>12,69%</t>
         </is>
       </c>
     </row>
@@ -1185,12 +1185,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>300748</t>
+          <t>300341</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>328556</t>
+          <t>328609</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1200,12 +1200,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>80,52%</t>
+          <t>80,41%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>87,96%</t>
+          <t>87,97%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1220,12 +1220,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>140099</t>
+          <t>141109</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>149144</t>
+          <t>149303</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1235,12 +1235,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>93,23%</t>
+          <t>93,9%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,25%</t>
+          <t>99,35%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1255,12 +1255,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>446086</t>
+          <t>443831</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>477165</t>
+          <t>475576</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1270,12 +1270,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>85,16%</t>
+          <t>84,73%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>91,1%</t>
+          <t>90,79%</t>
         </is>
       </c>
     </row>
@@ -1415,12 +1415,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>7878</t>
+          <t>8491</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>24266</t>
+          <t>26096</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1430,12 +1430,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>0,76%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2,18%</t>
+          <t>2,34%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1455,7 +1455,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>6829</t>
+          <t>6883</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1470,7 +1470,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>1,19%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1485,12 +1485,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>9585</t>
+          <t>9798</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>25946</t>
+          <t>28069</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1500,12 +1500,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,58%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>1,66%</t>
         </is>
       </c>
     </row>
@@ -1528,12 +1528,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>8544</t>
+          <t>9017</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>26549</t>
+          <t>25275</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1543,12 +1543,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,81%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>2,39%</t>
+          <t>2,27%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1563,12 +1563,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>3461</t>
+          <t>3655</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>16658</t>
+          <t>16004</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1578,12 +1578,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,63%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>2,88%</t>
+          <t>2,77%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1598,12 +1598,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>15118</t>
+          <t>14703</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>36385</t>
+          <t>35748</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1613,12 +1613,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>0,87%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>2,15%</t>
+          <t>2,11%</t>
         </is>
       </c>
     </row>
@@ -1641,12 +1641,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>22174</t>
+          <t>21249</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>42141</t>
+          <t>43992</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1656,12 +1656,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>1,99%</t>
+          <t>1,91%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>3,79%</t>
+          <t>3,95%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1676,12 +1676,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>1024</t>
+          <t>1053</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>9106</t>
+          <t>9737</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1696,7 +1696,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>1,58%</t>
+          <t>1,69%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1711,12 +1711,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>24477</t>
+          <t>25016</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>47471</t>
+          <t>48482</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1726,12 +1726,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>1,45%</t>
+          <t>1,48%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>2,81%</t>
+          <t>2,87%</t>
         </is>
       </c>
     </row>
@@ -1754,12 +1754,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>134852</t>
+          <t>135307</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>178292</t>
+          <t>179899</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1769,12 +1769,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>12,12%</t>
+          <t>12,16%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>16,02%</t>
+          <t>16,16%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1789,12 +1789,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>33343</t>
+          <t>32610</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>59905</t>
+          <t>60091</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>5,77%</t>
+          <t>5,64%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>10,37%</t>
+          <t>10,4%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1824,12 +1824,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>172917</t>
+          <t>175631</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>226689</t>
+          <t>228537</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1839,12 +1839,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>10,23%</t>
+          <t>10,39%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>13,41%</t>
+          <t>13,52%</t>
         </is>
       </c>
     </row>
@@ -1867,12 +1867,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>872601</t>
+          <t>869955</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>921003</t>
+          <t>922273</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1882,12 +1882,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>78,41%</t>
+          <t>78,17%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>82,76%</t>
+          <t>82,87%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1902,12 +1902,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>501844</t>
+          <t>500816</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>531438</t>
+          <t>532371</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1917,12 +1917,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>86,86%</t>
+          <t>86,68%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>91,98%</t>
+          <t>92,14%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1937,12 +1937,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1383129</t>
+          <t>1382669</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1444954</t>
+          <t>1445043</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1952,7 +1952,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>81,81%</t>
+          <t>81,78%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -2097,12 +2097,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>7531</t>
+          <t>7139</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>23252</t>
+          <t>21752</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2112,12 +2112,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>1,79%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>5,83%</t>
+          <t>5,46%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2132,12 +2132,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>2810</t>
+          <t>2840</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>14106</t>
+          <t>13150</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2147,12 +2147,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>0,98%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>4,87%</t>
+          <t>4,54%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2167,12 +2167,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>12403</t>
+          <t>11844</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>30799</t>
+          <t>29939</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2182,12 +2182,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>1,72%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>4,48%</t>
+          <t>4,35%</t>
         </is>
       </c>
     </row>
@@ -2210,12 +2210,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>10379</t>
+          <t>10555</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>28124</t>
+          <t>28975</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2225,12 +2225,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>2,65%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>7,05%</t>
+          <t>7,27%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2245,12 +2245,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3972</t>
+          <t>3925</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>16747</t>
+          <t>15793</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2260,12 +2260,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>1,37%</t>
+          <t>1,36%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>5,79%</t>
+          <t>5,46%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2280,12 +2280,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>16890</t>
+          <t>17173</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>36872</t>
+          <t>37106</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2295,12 +2295,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>2,45%</t>
+          <t>2,5%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>5,36%</t>
+          <t>5,39%</t>
         </is>
       </c>
     </row>
@@ -2328,7 +2328,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>25179</t>
+          <t>24174</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2343,7 +2343,7 @@
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>6,32%</t>
+          <t>6,06%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2358,12 +2358,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>2016</t>
+          <t>2012</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>11771</t>
+          <t>11802</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2378,7 +2378,7 @@
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>4,07%</t>
+          <t>4,08%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2393,12 +2393,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>13264</t>
+          <t>13149</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>32646</t>
+          <t>32195</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2408,12 +2408,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>1,93%</t>
+          <t>1,91%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>4,74%</t>
+          <t>4,68%</t>
         </is>
       </c>
     </row>
@@ -2436,12 +2436,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>65709</t>
+          <t>65363</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>99028</t>
+          <t>98307</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2451,12 +2451,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>16,48%</t>
+          <t>16,39%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>24,84%</t>
+          <t>24,66%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2471,12 +2471,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>21269</t>
+          <t>21440</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>42200</t>
+          <t>42434</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2486,12 +2486,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>7,35%</t>
+          <t>7,41%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>14,58%</t>
+          <t>14,66%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2506,12 +2506,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>92999</t>
+          <t>92614</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>131826</t>
+          <t>132232</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2521,12 +2521,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>13,51%</t>
+          <t>13,46%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>19,16%</t>
+          <t>19,21%</t>
         </is>
       </c>
     </row>
@@ -2549,12 +2549,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>253390</t>
+          <t>253700</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>292588</t>
+          <t>290269</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2564,12 +2564,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>63,55%</t>
+          <t>63,63%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>73,38%</t>
+          <t>72,8%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2584,12 +2584,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>223417</t>
+          <t>224679</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>250456</t>
+          <t>251137</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2599,12 +2599,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>77,18%</t>
+          <t>77,62%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>86,52%</t>
+          <t>86,75%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2619,12 +2619,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>485646</t>
+          <t>486057</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>530796</t>
+          <t>533533</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2634,12 +2634,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>70,57%</t>
+          <t>70,63%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>77,13%</t>
+          <t>77,53%</t>
         </is>
       </c>
     </row>
@@ -2779,12 +2779,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>20839</t>
+          <t>21475</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>43376</t>
+          <t>44181</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2794,12 +2794,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>1,14%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>2,34%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2814,12 +2814,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>4841</t>
+          <t>4769</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>17195</t>
+          <t>16554</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2829,12 +2829,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>0,47%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>1,69%</t>
+          <t>1,63%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2849,12 +2849,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>28684</t>
+          <t>27229</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>54770</t>
+          <t>54350</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2864,12 +2864,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>0,94%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>1,87%</t>
         </is>
       </c>
     </row>
@@ -2892,12 +2892,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>24830</t>
+          <t>24859</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>49246</t>
+          <t>49936</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2912,44 +2912,44 @@
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
+          <t>2,65%</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="K23" s="2" t="inlineStr">
+        <is>
+          <t>16457</t>
+        </is>
+      </c>
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>9543</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>26524</t>
+        </is>
+      </c>
+      <c r="N23" s="2" t="inlineStr">
+        <is>
+          <t>1,62%</t>
+        </is>
+      </c>
+      <c r="O23" s="2" t="inlineStr">
+        <is>
+          <t>0,94%</t>
+        </is>
+      </c>
+      <c r="P23" s="2" t="inlineStr">
+        <is>
           <t>2,61%</t>
         </is>
       </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="K23" s="2" t="inlineStr">
-        <is>
-          <t>16457</t>
-        </is>
-      </c>
-      <c r="L23" s="2" t="inlineStr">
-        <is>
-          <t>10008</t>
-        </is>
-      </c>
-      <c r="M23" s="2" t="inlineStr">
-        <is>
-          <t>27092</t>
-        </is>
-      </c>
-      <c r="N23" s="2" t="inlineStr">
-        <is>
-          <t>1,62%</t>
-        </is>
-      </c>
-      <c r="O23" s="2" t="inlineStr">
-        <is>
-          <t>0,98%</t>
-        </is>
-      </c>
-      <c r="P23" s="2" t="inlineStr">
-        <is>
-          <t>2,66%</t>
-        </is>
-      </c>
       <c r="Q23" s="2" t="inlineStr">
         <is>
           <t>48</t>
@@ -2962,12 +2962,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>39237</t>
+          <t>38716</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>69218</t>
+          <t>68742</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2977,12 +2977,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>1,35%</t>
+          <t>1,33%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>2,38%</t>
+          <t>2,37%</t>
         </is>
       </c>
     </row>
@@ -3005,12 +3005,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>38788</t>
+          <t>38088</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>65172</t>
+          <t>66490</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3020,12 +3020,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>2,06%</t>
+          <t>2,02%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>3,46%</t>
+          <t>3,53%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3040,12 +3040,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>4840</t>
+          <t>4951</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>17832</t>
+          <t>18738</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3055,12 +3055,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>0,49%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>1,75%</t>
+          <t>1,84%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3075,12 +3075,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>46727</t>
+          <t>46098</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>78312</t>
+          <t>75946</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3090,12 +3090,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>1,59%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>2,62%</t>
         </is>
       </c>
     </row>
@@ -3118,12 +3118,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>254559</t>
+          <t>254550</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>314118</t>
+          <t>313236</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3138,7 +3138,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>16,66%</t>
+          <t>16,62%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3153,12 +3153,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>62984</t>
+          <t>63185</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>96204</t>
+          <t>99190</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3168,12 +3168,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>6,19%</t>
+          <t>6,21%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>9,45%</t>
+          <t>9,75%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3188,12 +3188,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>330000</t>
+          <t>327103</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>399845</t>
+          <t>400040</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3203,7 +3203,7 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>11,37%</t>
+          <t>11,27%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
@@ -3231,12 +3231,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>1449227</t>
+          <t>1448314</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>1517880</t>
+          <t>1521671</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3246,12 +3246,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>76,88%</t>
+          <t>76,83%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>80,52%</t>
+          <t>80,72%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3266,12 +3266,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>881108</t>
+          <t>879254</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>922277</t>
+          <t>922111</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3281,12 +3281,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>86,59%</t>
+          <t>86,41%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>90,64%</t>
+          <t>90,62%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3301,12 +3301,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>2345920</t>
+          <t>2346319</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>2431779</t>
+          <t>2427134</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3316,12 +3316,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>80,82%</t>
+          <t>80,83%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>83,78%</t>
+          <t>83,62%</t>
         </is>
       </c>
     </row>
@@ -3497,7 +3497,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según el número de personas que trabajan bajo su responsabilidad en 2012</t>
+          <t>Población según el número de personas que trabajan bajo su responsabilidad en 2012 (tasa de respuesta: 99,23%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3697,7 +3697,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>6811</t>
+          <t>6856</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3712,7 +3712,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>3,7%</t>
+          <t>3,73%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3727,62 +3727,62 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R4" s="2" t="inlineStr">
+        <is>
+          <t>1948</t>
+        </is>
+      </c>
+      <c r="S4" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>2049</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>6881</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
+        <is>
+          <t>0,6%</t>
+        </is>
+      </c>
+      <c r="V4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>1,46%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>1948</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>6725</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>0,6%</t>
-        </is>
-      </c>
-      <c r="V4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,08%</t>
+          <t>2,12%</t>
         </is>
       </c>
     </row>
@@ -3810,7 +3810,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>4700</t>
+          <t>4961</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3825,7 +3825,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>2,55%</t>
+          <t>2,7%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3840,47 +3840,47 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q5" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R5" s="2" t="inlineStr">
+        <is>
+          <t>1085</t>
+        </is>
+      </c>
+      <c r="S5" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>2049</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t>1,46%</t>
-        </is>
-      </c>
-      <c r="Q5" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R5" s="2" t="inlineStr">
-        <is>
-          <t>1085</t>
-        </is>
-      </c>
-      <c r="S5" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>5413</t>
+          <t>5419</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3923,7 +3923,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>5749</t>
+          <t>5788</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -3938,7 +3938,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>3,12%</t>
+          <t>3,15%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -3958,7 +3958,7 @@
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>6182</t>
+          <t>7114</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3973,7 +3973,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>4,42%</t>
+          <t>5,08%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -3988,12 +3988,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>1046</t>
+          <t>1031</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>9706</t>
+          <t>9537</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4008,7 +4008,7 @@
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>3,0%</t>
+          <t>2,94%</t>
         </is>
       </c>
     </row>
@@ -4031,12 +4031,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>12734</t>
+          <t>13372</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>30342</t>
+          <t>31213</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4046,12 +4046,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>6,92%</t>
+          <t>7,27%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>16,49%</t>
+          <t>16,96%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4066,12 +4066,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>5902</t>
+          <t>5241</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>20183</t>
+          <t>20205</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4081,12 +4081,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>4,22%</t>
+          <t>3,74%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>14,42%</t>
+          <t>14,43%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4101,12 +4101,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>21743</t>
+          <t>21322</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>43700</t>
+          <t>43512</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4116,12 +4116,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>6,71%</t>
+          <t>6,58%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>13,49%</t>
+          <t>13,43%</t>
         </is>
       </c>
     </row>
@@ -4144,12 +4144,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>147253</t>
+          <t>147682</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>166750</t>
+          <t>166681</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4159,12 +4159,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>80,02%</t>
+          <t>80,25%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>90,62%</t>
+          <t>90,58%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4179,12 +4179,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>117765</t>
+          <t>117334</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>132719</t>
+          <t>132962</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4194,12 +4194,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>84,13%</t>
+          <t>83,82%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>94,81%</t>
+          <t>94,99%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4214,12 +4214,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>272853</t>
+          <t>273537</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>296231</t>
+          <t>296325</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4229,12 +4229,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>84,22%</t>
+          <t>84,43%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>91,43%</t>
+          <t>91,46%</t>
         </is>
       </c>
     </row>
@@ -4374,12 +4374,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>8690</t>
+          <t>8038</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>26774</t>
+          <t>26234</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4389,12 +4389,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>0,88%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2,93%</t>
+          <t>2,87%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4414,7 +4414,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>6830</t>
+          <t>6798</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4444,12 +4444,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>9791</t>
+          <t>10023</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>28977</t>
+          <t>29833</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4459,12 +4459,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>0,68%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,95%</t>
+          <t>2,01%</t>
         </is>
       </c>
     </row>
@@ -4487,12 +4487,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>5550</t>
+          <t>5641</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>20545</t>
+          <t>21271</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4502,12 +4502,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>2,25%</t>
+          <t>2,33%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4522,12 +4522,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>2980</t>
+          <t>2868</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>14375</t>
+          <t>14825</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4537,12 +4537,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>2,51%</t>
+          <t>2,59%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4557,12 +4557,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>10336</t>
+          <t>10276</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>30256</t>
+          <t>30107</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4572,12 +4572,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,69%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>2,04%</t>
+          <t>2,03%</t>
         </is>
       </c>
     </row>
@@ -4600,12 +4600,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>14725</t>
+          <t>14624</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>34445</t>
+          <t>33330</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -4615,12 +4615,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>3,77%</t>
+          <t>3,65%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -4635,12 +4635,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>3757</t>
+          <t>3067</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>16085</t>
+          <t>15674</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -4650,12 +4650,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>0,54%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>2,81%</t>
+          <t>2,74%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -4670,12 +4670,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>20078</t>
+          <t>21517</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>42551</t>
+          <t>45580</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -4685,12 +4685,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>1,35%</t>
+          <t>1,45%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>2,87%</t>
+          <t>3,07%</t>
         </is>
       </c>
     </row>
@@ -4713,12 +4713,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>133897</t>
+          <t>135197</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>179603</t>
+          <t>181448</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4728,12 +4728,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>14,67%</t>
+          <t>14,82%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>19,68%</t>
+          <t>19,88%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4748,12 +4748,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>35120</t>
+          <t>36122</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>63583</t>
+          <t>63871</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4763,12 +4763,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>6,14%</t>
+          <t>6,32%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>11,12%</t>
+          <t>11,17%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4783,12 +4783,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>178571</t>
+          <t>177062</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>235258</t>
+          <t>230998</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>12,03%</t>
+          <t>11,93%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>15,85%</t>
+          <t>15,56%</t>
         </is>
       </c>
     </row>
@@ -4826,12 +4826,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>680339</t>
+          <t>677410</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>732203</t>
+          <t>729433</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4841,12 +4841,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>74,55%</t>
+          <t>74,23%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>80,24%</t>
+          <t>79,93%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4861,12 +4861,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>490764</t>
+          <t>490155</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>521633</t>
+          <t>521338</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4876,12 +4876,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>85,81%</t>
+          <t>85,7%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>91,21%</t>
+          <t>91,15%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4896,12 +4896,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1181369</t>
+          <t>1183447</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1245794</t>
+          <t>1246277</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4911,12 +4911,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>79,58%</t>
+          <t>79,72%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>83,92%</t>
+          <t>83,95%</t>
         </is>
       </c>
     </row>
@@ -5056,12 +5056,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>5945</t>
+          <t>6103</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>23567</t>
+          <t>25559</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5071,12 +5071,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>1,94%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>7,47%</t>
+          <t>8,11%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5091,12 +5091,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>934</t>
+          <t>938</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>8926</t>
+          <t>8192</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5111,7 +5111,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>3,8%</t>
+          <t>3,49%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5126,12 +5126,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>8166</t>
+          <t>7125</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>27411</t>
+          <t>25358</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5141,12 +5141,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>1,29%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>4,98%</t>
+          <t>4,61%</t>
         </is>
       </c>
     </row>
@@ -5169,12 +5169,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>6376</t>
+          <t>6540</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>22397</t>
+          <t>21148</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5184,12 +5184,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>2,02%</t>
+          <t>2,07%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>7,1%</t>
+          <t>6,71%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5204,12 +5204,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>956</t>
+          <t>984</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>8272</t>
+          <t>8374</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5219,12 +5219,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,42%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>3,52%</t>
+          <t>3,57%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5239,12 +5239,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>8568</t>
+          <t>8208</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>24120</t>
+          <t>23979</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5254,12 +5254,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>1,56%</t>
+          <t>1,49%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>4,38%</t>
+          <t>4,36%</t>
         </is>
       </c>
     </row>
@@ -5282,12 +5282,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>7875</t>
+          <t>8199</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>23893</t>
+          <t>24626</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -5297,12 +5297,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>2,6%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>7,58%</t>
+          <t>7,81%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -5322,7 +5322,7 @@
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>4348</t>
+          <t>5439</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -5337,7 +5337,7 @@
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>1,85%</t>
+          <t>2,32%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -5352,12 +5352,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>9199</t>
+          <t>8379</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>26172</t>
+          <t>26150</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -5367,12 +5367,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>1,52%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>4,76%</t>
+          <t>4,75%</t>
         </is>
       </c>
     </row>
@@ -5395,12 +5395,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>66474</t>
+          <t>68152</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>99671</t>
+          <t>100653</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5410,12 +5410,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>21,08%</t>
+          <t>21,61%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>31,61%</t>
+          <t>31,92%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5430,12 +5430,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>20133</t>
+          <t>19958</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>43567</t>
+          <t>43625</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5445,12 +5445,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>8,57%</t>
+          <t>8,5%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>18,55%</t>
+          <t>18,57%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5465,12 +5465,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>92984</t>
+          <t>94111</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>134838</t>
+          <t>136339</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5480,12 +5480,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>16,9%</t>
+          <t>17,1%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>24,51%</t>
+          <t>24,78%</t>
         </is>
       </c>
     </row>
@@ -5508,12 +5508,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>175763</t>
+          <t>176142</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>212845</t>
+          <t>212051</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5523,12 +5523,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>55,74%</t>
+          <t>55,86%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>67,5%</t>
+          <t>67,25%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5543,12 +5543,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>183244</t>
+          <t>182955</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>209168</t>
+          <t>209402</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5558,12 +5558,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>78,01%</t>
+          <t>77,89%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>89,05%</t>
+          <t>89,15%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5578,12 +5578,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>368184</t>
+          <t>367733</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>413748</t>
+          <t>415799</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5593,12 +5593,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>66,92%</t>
+          <t>66,83%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>75,2%</t>
+          <t>75,57%</t>
         </is>
       </c>
     </row>
@@ -5738,12 +5738,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>19223</t>
+          <t>19958</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>43307</t>
+          <t>45656</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5753,12 +5753,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>1,41%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>3,07%</t>
+          <t>3,23%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5773,12 +5773,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>1903</t>
+          <t>1948</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>10575</t>
+          <t>11831</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5788,12 +5788,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>0,21%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>1,25%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5808,12 +5808,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>23808</t>
+          <t>23282</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>50689</t>
+          <t>49628</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5823,12 +5823,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>0,99%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>2,15%</t>
+          <t>2,1%</t>
         </is>
       </c>
     </row>
@@ -5851,12 +5851,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>15266</t>
+          <t>15503</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>37070</t>
+          <t>35956</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5866,12 +5866,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>2,63%</t>
+          <t>2,55%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5886,12 +5886,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>5097</t>
+          <t>5048</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>18911</t>
+          <t>18571</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5901,12 +5901,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>0,54%</t>
+          <t>0,53%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>1,96%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5921,12 +5921,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>24031</t>
+          <t>23374</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>49096</t>
+          <t>47673</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5936,12 +5936,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>0,99%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>2,08%</t>
+          <t>2,02%</t>
         </is>
       </c>
     </row>
@@ -5964,12 +5964,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>27563</t>
+          <t>27856</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>52850</t>
+          <t>52956</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -5979,12 +5979,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>1,95%</t>
+          <t>1,97%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>3,74%</t>
+          <t>3,75%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -5999,12 +5999,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>5803</t>
+          <t>5770</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>19549</t>
+          <t>19045</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -6019,7 +6019,7 @@
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>2,06%</t>
+          <t>2,01%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -6034,12 +6034,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>36062</t>
+          <t>36526</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>66177</t>
+          <t>65436</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -6049,12 +6049,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>1,55%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>2,81%</t>
+          <t>2,77%</t>
         </is>
       </c>
     </row>
@@ -6077,12 +6077,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>231351</t>
+          <t>228786</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>291023</t>
+          <t>291393</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6092,12 +6092,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>16,39%</t>
+          <t>16,2%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>20,61%</t>
+          <t>20,64%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6112,12 +6112,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>70170</t>
+          <t>73081</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>111806</t>
+          <t>109883</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6127,12 +6127,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>7,41%</t>
+          <t>7,72%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>11,81%</t>
+          <t>11,61%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6147,12 +6147,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>314584</t>
+          <t>313431</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>388287</t>
+          <t>383995</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6162,12 +6162,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>13,34%</t>
+          <t>13,29%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>16,46%</t>
+          <t>16,28%</t>
         </is>
       </c>
     </row>
@@ -6190,12 +6190,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>1024458</t>
+          <t>1023448</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>1092548</t>
+          <t>1092986</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6205,12 +6205,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>72,56%</t>
+          <t>72,49%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>77,38%</t>
+          <t>77,41%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6225,12 +6225,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>805787</t>
+          <t>809602</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>852908</t>
+          <t>850409</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6240,12 +6240,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>85,11%</t>
+          <t>85,51%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>90,08%</t>
+          <t>89,82%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6260,12 +6260,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1849540</t>
+          <t>1853411</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1931863</t>
+          <t>1931145</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6275,12 +6275,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>78,41%</t>
+          <t>78,58%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>81,9%</t>
+          <t>81,87%</t>
         </is>
       </c>
     </row>
@@ -6456,7 +6456,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según el número de personas que trabajan bajo su responsabilidad en 2016</t>
+          <t>Población según el número de personas que trabajan bajo su responsabilidad en 2016 (tasa de respuesta: 99,27%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -6651,97 +6651,97 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>2033</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>1,45%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
+      <c r="O4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K4" s="2" t="inlineStr">
+      <c r="R4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>1891</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
+      <c r="S4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>2,66%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>1995</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -6764,97 +6764,97 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>2033</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>1,45%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
+      <c r="O5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q5" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K5" s="2" t="inlineStr">
+      <c r="R5" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>1891</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
+      <c r="S5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U5" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t>2,66%</t>
-        </is>
-      </c>
-      <c r="Q5" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R5" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S5" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T5" s="2" t="inlineStr">
-        <is>
-          <t>1995</t>
-        </is>
-      </c>
-      <c r="U5" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -6877,12 +6877,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>1903</t>
+          <t>1945</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>10269</t>
+          <t>11421</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -6892,12 +6892,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>1,39%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>7,34%</t>
+          <t>8,16%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -6917,7 +6917,7 @@
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>5472</t>
+          <t>4639</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6932,7 +6932,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>7,7%</t>
+          <t>6,52%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -6947,12 +6947,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>2122</t>
+          <t>2081</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>13337</t>
+          <t>13393</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6962,12 +6962,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>0,99%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>6,32%</t>
+          <t>6,35%</t>
         </is>
       </c>
     </row>
@@ -6990,12 +6990,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>10750</t>
+          <t>11013</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>26735</t>
+          <t>27668</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7005,12 +7005,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>7,68%</t>
+          <t>7,87%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>19,1%</t>
+          <t>19,77%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7025,12 +7025,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>876</t>
+          <t>874</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>8299</t>
+          <t>8202</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7045,7 +7045,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>11,67%</t>
+          <t>11,53%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7060,12 +7060,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>14109</t>
+          <t>13778</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>32037</t>
+          <t>31862</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7075,12 +7075,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>6,68%</t>
+          <t>6,53%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>15,18%</t>
+          <t>15,1%</t>
         </is>
       </c>
     </row>
@@ -7103,12 +7103,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>107020</t>
+          <t>107061</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>125046</t>
+          <t>124970</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7118,12 +7118,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>76,46%</t>
+          <t>76,49%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>89,34%</t>
+          <t>89,29%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7138,12 +7138,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>61085</t>
+          <t>61350</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>69994</t>
+          <t>70043</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7153,12 +7153,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>85,91%</t>
+          <t>86,28%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>98,44%</t>
+          <t>98,51%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7173,12 +7173,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>171885</t>
+          <t>172680</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>192195</t>
+          <t>191762</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7188,12 +7188,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>81,44%</t>
+          <t>81,81%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>91,06%</t>
+          <t>90,85%</t>
         </is>
       </c>
     </row>
@@ -7333,12 +7333,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>2199</t>
+          <t>2166</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>14193</t>
+          <t>14468</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7353,7 +7353,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>1,55%</t>
+          <t>1,58%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7368,12 +7368,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>1873</t>
+          <t>1887</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>11499</t>
+          <t>12957</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7388,7 +7388,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>1,77%</t>
+          <t>1,99%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7403,12 +7403,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>6238</t>
+          <t>6486</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>22249</t>
+          <t>20746</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7418,12 +7418,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,41%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,32%</t>
         </is>
       </c>
     </row>
@@ -7446,12 +7446,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>4933</t>
+          <t>5118</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>20704</t>
+          <t>19926</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7461,12 +7461,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,54%</t>
+          <t>0,56%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>2,26%</t>
+          <t>2,17%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7486,7 +7486,7 @@
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>5325</t>
+          <t>5095</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7501,7 +7501,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>0,78%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7516,12 +7516,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>5986</t>
+          <t>5872</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>21945</t>
+          <t>20738</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7531,12 +7531,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>0,37%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>1,32%</t>
         </is>
       </c>
     </row>
@@ -7559,12 +7559,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>12086</t>
+          <t>12628</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>32255</t>
+          <t>31561</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -7574,12 +7574,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,38%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>3,51%</t>
+          <t>3,44%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -7594,12 +7594,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>3744</t>
+          <t>3176</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>16826</t>
+          <t>15962</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -7609,12 +7609,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>0,49%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>2,59%</t>
+          <t>2,46%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -7629,12 +7629,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>18826</t>
+          <t>18355</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>42468</t>
+          <t>41114</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -7644,12 +7644,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,17%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>2,71%</t>
+          <t>2,62%</t>
         </is>
       </c>
     </row>
@@ -7672,12 +7672,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>83530</t>
+          <t>80754</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>124031</t>
+          <t>120522</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7687,12 +7687,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>9,1%</t>
+          <t>8,8%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>13,51%</t>
+          <t>13,13%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7707,12 +7707,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>30986</t>
+          <t>30020</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>55834</t>
+          <t>55688</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7722,12 +7722,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>4,77%</t>
+          <t>4,62%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>8,6%</t>
+          <t>8,57%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7742,12 +7742,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>120391</t>
+          <t>121504</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>168794</t>
+          <t>167696</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7757,12 +7757,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>7,68%</t>
+          <t>7,75%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>10,77%</t>
+          <t>10,7%</t>
         </is>
       </c>
     </row>
@@ -7785,12 +7785,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>756088</t>
+          <t>754467</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>800201</t>
+          <t>801790</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7800,12 +7800,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>82,35%</t>
+          <t>82,18%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>87,16%</t>
+          <t>87,33%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7820,12 +7820,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>579260</t>
+          <t>578594</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>606836</t>
+          <t>606876</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7835,7 +7835,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>89,17%</t>
+          <t>89,07%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -7855,12 +7855,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1342306</t>
+          <t>1346543</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1399119</t>
+          <t>1397164</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7870,12 +7870,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>85,62%</t>
+          <t>85,89%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>89,25%</t>
+          <t>89,12%</t>
         </is>
       </c>
     </row>
@@ -8015,12 +8015,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>5903</t>
+          <t>5798</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>21251</t>
+          <t>20179</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8030,12 +8030,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>1,67%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>6,11%</t>
+          <t>5,8%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8055,7 +8055,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>7030</t>
+          <t>5985</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8070,7 +8070,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>1,96%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8085,12 +8085,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>7317</t>
+          <t>6872</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>22408</t>
+          <t>22492</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8100,12 +8100,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>1,05%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>3,43%</t>
+          <t>3,44%</t>
         </is>
       </c>
     </row>
@@ -8128,12 +8128,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3009</t>
+          <t>3145</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>16371</t>
+          <t>15651</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8143,12 +8143,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>4,7%</t>
+          <t>4,5%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8163,12 +8163,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>1813</t>
+          <t>1855</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>10418</t>
+          <t>10398</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8178,12 +8178,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>0,61%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>3,41%</t>
+          <t>3,4%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8198,12 +8198,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>6908</t>
+          <t>6978</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>22048</t>
+          <t>22414</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8213,12 +8213,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>1,07%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>3,37%</t>
+          <t>3,43%</t>
         </is>
       </c>
     </row>
@@ -8241,12 +8241,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>11916</t>
+          <t>11422</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>30182</t>
+          <t>29979</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -8256,12 +8256,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>3,42%</t>
+          <t>3,28%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>8,67%</t>
+          <t>8,61%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -8276,12 +8276,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>3732</t>
+          <t>3526</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>16056</t>
+          <t>15508</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -8291,12 +8291,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>1,15%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>5,25%</t>
+          <t>5,07%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -8311,12 +8311,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>17133</t>
+          <t>16826</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>39238</t>
+          <t>38665</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -8326,12 +8326,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>2,62%</t>
+          <t>2,57%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>6,0%</t>
+          <t>5,92%</t>
         </is>
       </c>
     </row>
@@ -8354,12 +8354,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>43155</t>
+          <t>42528</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>72838</t>
+          <t>72700</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -8369,12 +8369,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>12,4%</t>
+          <t>12,22%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>20,93%</t>
+          <t>20,89%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -8389,12 +8389,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>19960</t>
+          <t>19108</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>40239</t>
+          <t>40834</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -8404,12 +8404,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>6,53%</t>
+          <t>6,25%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>13,17%</t>
+          <t>13,36%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -8424,12 +8424,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>69438</t>
+          <t>70081</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>106776</t>
+          <t>105832</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -8439,12 +8439,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>10,62%</t>
+          <t>10,72%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>16,34%</t>
+          <t>16,19%</t>
         </is>
       </c>
     </row>
@@ -8467,12 +8467,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>233290</t>
+          <t>234895</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>269581</t>
+          <t>270113</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -8482,12 +8482,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>67,03%</t>
+          <t>67,49%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>77,46%</t>
+          <t>77,61%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -8502,12 +8502,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>248714</t>
+          <t>247798</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>273010</t>
+          <t>273261</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -8517,12 +8517,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>81,38%</t>
+          <t>81,08%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>89,33%</t>
+          <t>89,42%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -8537,12 +8537,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>490972</t>
+          <t>492023</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>536066</t>
+          <t>535162</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -8552,12 +8552,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>75,11%</t>
+          <t>75,27%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>82,01%</t>
+          <t>81,87%</t>
         </is>
       </c>
     </row>
@@ -8697,12 +8697,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>10457</t>
+          <t>10689</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>28758</t>
+          <t>29006</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8712,12 +8712,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>0,76%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>2,05%</t>
+          <t>2,06%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8732,12 +8732,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>3398</t>
+          <t>3490</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>15000</t>
+          <t>14678</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8747,12 +8747,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>0,33%</t>
+          <t>0,34%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>1,46%</t>
+          <t>1,43%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8767,12 +8767,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>16582</t>
+          <t>17067</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>37827</t>
+          <t>38958</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8782,12 +8782,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>1,56%</t>
+          <t>1,6%</t>
         </is>
       </c>
     </row>
@@ -8810,12 +8810,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>11024</t>
+          <t>11111</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>31167</t>
+          <t>31537</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8825,12 +8825,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>0,79%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>2,22%</t>
+          <t>2,24%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8845,12 +8845,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>2672</t>
+          <t>1894</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>11335</t>
+          <t>11998</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8860,12 +8860,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>0,26%</t>
+          <t>0,18%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>1,17%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8880,12 +8880,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>16036</t>
+          <t>15709</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>36659</t>
+          <t>36321</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8895,12 +8895,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>0,65%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>1,49%</t>
         </is>
       </c>
     </row>
@@ -8923,12 +8923,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>31349</t>
+          <t>31368</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>58402</t>
+          <t>59422</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -8943,7 +8943,7 @@
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>4,15%</t>
+          <t>4,23%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -8958,12 +8958,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>10469</t>
+          <t>10087</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>26110</t>
+          <t>26709</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -8973,12 +8973,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>0,98%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>2,54%</t>
+          <t>2,6%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -8993,12 +8993,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>45366</t>
+          <t>45804</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>79284</t>
+          <t>79677</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -9008,12 +9008,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>1,87%</t>
+          <t>1,88%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>3,26%</t>
+          <t>3,28%</t>
         </is>
       </c>
     </row>
@@ -9036,12 +9036,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>152082</t>
+          <t>150671</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>204339</t>
+          <t>203912</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9051,12 +9051,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>10,82%</t>
+          <t>10,72%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>14,53%</t>
+          <t>14,5%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9071,12 +9071,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>58587</t>
+          <t>58290</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>94130</t>
+          <t>92090</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9086,12 +9086,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>5,71%</t>
+          <t>5,68%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>9,17%</t>
+          <t>8,97%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9106,12 +9106,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>218074</t>
+          <t>222615</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>279669</t>
+          <t>283539</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9121,12 +9121,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>8,97%</t>
+          <t>9,15%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>11,5%</t>
+          <t>11,66%</t>
         </is>
       </c>
     </row>
@@ -9149,12 +9149,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>1117084</t>
+          <t>1119010</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>1178539</t>
+          <t>1179113</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9164,12 +9164,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>79,44%</t>
+          <t>79,58%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>83,81%</t>
+          <t>83,86%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9184,12 +9184,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>899577</t>
+          <t>901864</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>940248</t>
+          <t>940101</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9199,12 +9199,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>87,65%</t>
+          <t>87,88%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>91,62%</t>
+          <t>91,6%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9219,12 +9219,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>2036879</t>
+          <t>2028049</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>2106032</t>
+          <t>2102251</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9234,12 +9234,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>83,74%</t>
+          <t>83,38%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>86,58%</t>
+          <t>86,43%</t>
         </is>
       </c>
     </row>
@@ -9415,7 +9415,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según el número de personas que trabajan bajo su responsabilidad en 2023</t>
+          <t>Población según el número de personas que trabajan bajo su responsabilidad en 2023 (tasa de respuesta: 99,17%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -9610,97 +9610,97 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>1772</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>1,34%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
+      <c r="O4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K4" s="2" t="inlineStr">
+      <c r="R4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>1283</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
+      <c r="S4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>1,55%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>1552</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -9723,12 +9723,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>2356</t>
+          <t>1985</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>13300</t>
+          <t>13261</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -9738,12 +9738,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,78%</t>
+          <t>1,5%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>10,07%</t>
+          <t>10,04%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -9758,12 +9758,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>1283</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -9773,12 +9773,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>1,55%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -9793,12 +9793,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>2072</t>
+          <t>1958</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>12919</t>
+          <t>13708</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -9808,12 +9808,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>0,91%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>6,01%</t>
+          <t>6,37%</t>
         </is>
       </c>
     </row>
@@ -9841,7 +9841,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>4679</t>
+          <t>5401</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -9856,7 +9856,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>3,54%</t>
+          <t>4,09%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -9871,62 +9871,62 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O6" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P6" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q6" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R6" s="2" t="inlineStr">
+        <is>
+          <t>1401</t>
+        </is>
+      </c>
+      <c r="S6" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>1283</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr">
+      <c r="T6" s="2" t="inlineStr">
+        <is>
+          <t>5110</t>
+        </is>
+      </c>
+      <c r="U6" s="2" t="inlineStr">
+        <is>
+          <t>0,65%</t>
+        </is>
+      </c>
+      <c r="V6" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O6" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P6" s="2" t="inlineStr">
-        <is>
-          <t>1,55%</t>
-        </is>
-      </c>
-      <c r="Q6" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R6" s="2" t="inlineStr">
-        <is>
-          <t>1401</t>
-        </is>
-      </c>
-      <c r="S6" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T6" s="2" t="inlineStr">
-        <is>
-          <t>4576</t>
-        </is>
-      </c>
-      <c r="U6" s="2" t="inlineStr">
-        <is>
-          <t>0,65%</t>
-        </is>
-      </c>
-      <c r="V6" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>2,13%</t>
+          <t>2,38%</t>
         </is>
       </c>
     </row>
@@ -9949,12 +9949,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2282</t>
+          <t>2109</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>14569</t>
+          <t>15667</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -9964,12 +9964,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,73%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>11,03%</t>
+          <t>11,86%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -9984,12 +9984,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>2614</t>
+          <t>2582</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>10441</t>
+          <t>10616</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -9999,12 +9999,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>3,15%</t>
+          <t>3,11%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>12,59%</t>
+          <t>12,8%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -10019,12 +10019,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>6676</t>
+          <t>6429</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>20174</t>
+          <t>20560</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -10034,12 +10034,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>3,1%</t>
+          <t>2,99%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>9,38%</t>
+          <t>9,56%</t>
         </is>
       </c>
     </row>
@@ -10062,12 +10062,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>109466</t>
+          <t>109166</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>124633</t>
+          <t>124446</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -10077,12 +10077,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>82,86%</t>
+          <t>82,64%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>94,35%</t>
+          <t>94,2%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -10097,12 +10097,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>72508</t>
+          <t>72333</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>80335</t>
+          <t>80367</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -10112,12 +10112,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>87,41%</t>
+          <t>87,2%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>96,85%</t>
+          <t>96,89%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -10132,12 +10132,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>185613</t>
+          <t>185448</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>203399</t>
+          <t>203205</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -10147,12 +10147,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>86,31%</t>
+          <t>86,23%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>94,58%</t>
+          <t>94,49%</t>
         </is>
       </c>
     </row>
@@ -10292,12 +10292,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>9431</t>
+          <t>9094</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>32513</t>
+          <t>31378</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -10307,12 +10307,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,66%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2,36%</t>
+          <t>2,28%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -10327,12 +10327,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>561</t>
+          <t>602</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>5416</t>
+          <t>5754</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -10347,7 +10347,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,61%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -10362,12 +10362,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>13339</t>
+          <t>12625</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>33994</t>
+          <t>33727</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -10377,12 +10377,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,54%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>1,45%</t>
         </is>
       </c>
     </row>
@@ -10405,12 +10405,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>12607</t>
+          <t>11866</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>791389</t>
+          <t>724200</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -10420,12 +10420,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>57,48%</t>
+          <t>52,6%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -10440,12 +10440,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>2829</t>
+          <t>2692</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>11521</t>
+          <t>11749</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -10455,12 +10455,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,29%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>1,25%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -10475,12 +10475,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>17631</t>
+          <t>17590</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>963863</t>
+          <t>786734</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -10495,7 +10495,7 @@
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>41,54%</t>
+          <t>33,91%</t>
         </is>
       </c>
     </row>
@@ -10518,12 +10518,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>18702</t>
+          <t>17931</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>53283</t>
+          <t>52554</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -10533,12 +10533,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>3,87%</t>
+          <t>3,82%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -10553,12 +10553,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>5256</t>
+          <t>4894</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>15993</t>
+          <t>16245</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -10568,12 +10568,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>0,52%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>1,72%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -10588,12 +10588,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>28271</t>
+          <t>27657</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>61674</t>
+          <t>62946</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -10603,12 +10603,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>1,19%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>2,66%</t>
+          <t>2,71%</t>
         </is>
       </c>
     </row>
@@ -10631,12 +10631,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>61717</t>
+          <t>58369</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>136935</t>
+          <t>135290</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -10646,82 +10646,82 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
+          <t>4,24%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>9,83%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>71</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>41960</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>30899</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>54770</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>4,45%</t>
+        </is>
+      </c>
+      <c r="O13" s="2" t="inlineStr">
+        <is>
+          <t>3,28%</t>
+        </is>
+      </c>
+      <c r="P13" s="2" t="inlineStr">
+        <is>
+          <t>5,81%</t>
+        </is>
+      </c>
+      <c r="Q13" s="2" t="inlineStr">
+        <is>
+          <t>182</t>
+        </is>
+      </c>
+      <c r="R13" s="2" t="inlineStr">
+        <is>
+          <t>146861</t>
+        </is>
+      </c>
+      <c r="S13" s="2" t="inlineStr">
+        <is>
+          <t>103987</t>
+        </is>
+      </c>
+      <c r="T13" s="2" t="inlineStr">
+        <is>
+          <t>175998</t>
+        </is>
+      </c>
+      <c r="U13" s="2" t="inlineStr">
+        <is>
+          <t>6,33%</t>
+        </is>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
+        <is>
           <t>4,48%</t>
         </is>
       </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>9,95%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>71</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>41960</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>30863</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>54498</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>4,45%</t>
-        </is>
-      </c>
-      <c r="O13" s="2" t="inlineStr">
-        <is>
-          <t>3,27%</t>
-        </is>
-      </c>
-      <c r="P13" s="2" t="inlineStr">
-        <is>
-          <t>5,78%</t>
-        </is>
-      </c>
-      <c r="Q13" s="2" t="inlineStr">
-        <is>
-          <t>182</t>
-        </is>
-      </c>
-      <c r="R13" s="2" t="inlineStr">
-        <is>
-          <t>146861</t>
-        </is>
-      </c>
-      <c r="S13" s="2" t="inlineStr">
-        <is>
-          <t>103082</t>
-        </is>
-      </c>
-      <c r="T13" s="2" t="inlineStr">
-        <is>
-          <t>177906</t>
-        </is>
-      </c>
-      <c r="U13" s="2" t="inlineStr">
-        <is>
-          <t>6,33%</t>
-        </is>
-      </c>
-      <c r="V13" s="2" t="inlineStr">
-        <is>
-          <t>4,44%</t>
-        </is>
-      </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>7,67%</t>
+          <t>7,59%</t>
         </is>
       </c>
     </row>
@@ -10744,12 +10744,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>503297</t>
+          <t>558977</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1177270</t>
+          <t>1176509</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -10759,12 +10759,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>36,55%</t>
+          <t>40,6%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>85,5%</t>
+          <t>85,45%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -10779,12 +10779,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>868175</t>
+          <t>867516</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>898470</t>
+          <t>898647</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -10794,12 +10794,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>92,03%</t>
+          <t>91,96%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>95,25%</t>
+          <t>95,27%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -10814,12 +10814,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1242539</t>
+          <t>1366730</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>2075222</t>
+          <t>2073506</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -10829,12 +10829,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>53,55%</t>
+          <t>58,9%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>89,44%</t>
+          <t>89,37%</t>
         </is>
       </c>
     </row>
@@ -10974,12 +10974,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>12941</t>
+          <t>12397</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>31721</t>
+          <t>30359</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -10989,12 +10989,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2,92%</t>
+          <t>2,79%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>7,15%</t>
+          <t>6,84%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -11009,12 +11009,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>3680</t>
+          <t>3167</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>13524</t>
+          <t>12135</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -11024,12 +11024,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,85%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>3,11%</t>
+          <t>2,79%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -11044,12 +11044,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>18436</t>
+          <t>17976</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>39550</t>
+          <t>37604</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -11059,12 +11059,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>2,04%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>4,5%</t>
+          <t>4,28%</t>
         </is>
       </c>
     </row>
@@ -11087,12 +11087,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>5680</t>
+          <t>5587</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>19241</t>
+          <t>19899</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -11102,12 +11102,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>1,26%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>4,33%</t>
+          <t>4,48%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -11122,12 +11122,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>6033</t>
+          <t>5872</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>16456</t>
+          <t>16337</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -11137,12 +11137,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>1,35%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>3,78%</t>
+          <t>3,75%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -11157,12 +11157,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>14012</t>
+          <t>13389</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>32806</t>
+          <t>31149</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -11172,12 +11172,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>1,52%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>3,73%</t>
+          <t>3,54%</t>
         </is>
       </c>
     </row>
@@ -11200,12 +11200,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>14346</t>
+          <t>14868</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>32827</t>
+          <t>32673</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -11215,12 +11215,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>3,23%</t>
+          <t>3,35%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>7,4%</t>
+          <t>7,36%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -11235,12 +11235,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>5993</t>
+          <t>6123</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>17263</t>
+          <t>16579</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -11250,12 +11250,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>1,41%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>3,97%</t>
+          <t>3,81%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -11270,12 +11270,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>24198</t>
+          <t>24072</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>45322</t>
+          <t>45177</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -11285,12 +11285,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>2,75%</t>
+          <t>2,74%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>5,16%</t>
+          <t>5,14%</t>
         </is>
       </c>
     </row>
@@ -11313,12 +11313,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>51992</t>
+          <t>51948</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>84331</t>
+          <t>84937</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -11328,12 +11328,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>11,71%</t>
+          <t>11,7%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>19,0%</t>
+          <t>19,14%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -11348,12 +11348,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>32041</t>
+          <t>31110</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>52211</t>
+          <t>53144</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -11363,12 +11363,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>7,36%</t>
+          <t>7,15%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>12,0%</t>
+          <t>12,21%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -11383,12 +11383,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>89082</t>
+          <t>88990</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>127571</t>
+          <t>127580</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -11398,7 +11398,7 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>10,13%</t>
+          <t>10,12%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
@@ -11426,12 +11426,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>302066</t>
+          <t>302056</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>340577</t>
+          <t>342459</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -11441,12 +11441,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>68,06%</t>
+          <t>68,05%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>76,73%</t>
+          <t>77,16%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -11461,12 +11461,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>353503</t>
+          <t>353250</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>379187</t>
+          <t>379035</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -11476,12 +11476,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>81,22%</t>
+          <t>81,16%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>87,12%</t>
+          <t>87,09%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -11496,12 +11496,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>669249</t>
+          <t>666642</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>714724</t>
+          <t>712300</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -11511,12 +11511,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>76,13%</t>
+          <t>75,83%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>81,3%</t>
+          <t>81,03%</t>
         </is>
       </c>
     </row>
@@ -11656,12 +11656,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>24644</t>
+          <t>25671</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>56199</t>
+          <t>56389</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -11671,12 +11671,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>1,31%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>2,88%</t>
+          <t>2,89%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -11691,12 +11691,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>4705</t>
+          <t>4546</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>15205</t>
+          <t>14930</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -11706,12 +11706,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>0,32%</t>
+          <t>0,31%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>1,02%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -11726,12 +11726,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>35404</t>
+          <t>33451</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>67733</t>
+          <t>65265</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -11741,12 +11741,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>0,98%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>1,98%</t>
+          <t>1,91%</t>
         </is>
       </c>
     </row>
@@ -11769,12 +11769,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>30631</t>
+          <t>30007</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>747224</t>
+          <t>871801</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -11784,12 +11784,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>1,57%</t>
+          <t>1,54%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>38,26%</t>
+          <t>44,64%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -11804,12 +11804,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>10849</t>
+          <t>10652</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>24021</t>
+          <t>24327</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -11819,12 +11819,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>1,66%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -11839,12 +11839,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>44202</t>
+          <t>43823</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>993842</t>
+          <t>944920</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -11854,12 +11854,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>1,28%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>29,11%</t>
+          <t>27,67%</t>
         </is>
       </c>
     </row>
@@ -11882,12 +11882,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>38247</t>
+          <t>36444</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>79792</t>
+          <t>80676</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -11897,12 +11897,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>1,96%</t>
+          <t>1,87%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>4,09%</t>
+          <t>4,13%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -11917,12 +11917,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>12802</t>
+          <t>13291</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>27707</t>
+          <t>28540</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -11932,12 +11932,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>0,91%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>1,95%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -11952,12 +11952,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>56952</t>
+          <t>58549</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>99818</t>
+          <t>101512</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -11967,12 +11967,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>1,71%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>2,92%</t>
+          <t>2,97%</t>
         </is>
       </c>
     </row>
@@ -11995,12 +11995,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>123197</t>
+          <t>118333</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>214993</t>
+          <t>217210</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -12010,12 +12010,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>6,31%</t>
+          <t>6,06%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>11,01%</t>
+          <t>11,12%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -12030,12 +12030,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>73347</t>
+          <t>72461</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>107913</t>
+          <t>105677</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -12045,12 +12045,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>5,02%</t>
+          <t>4,96%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>7,38%</t>
+          <t>7,23%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -12065,12 +12065,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>207473</t>
+          <t>202738</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>309537</t>
+          <t>304356</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -12080,12 +12080,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>6,08%</t>
+          <t>5,94%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>9,07%</t>
+          <t>8,91%</t>
         </is>
       </c>
     </row>
@@ -12108,12 +12108,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>989013</t>
+          <t>905202</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>1614638</t>
+          <t>1616591</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -12123,12 +12123,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>50,64%</t>
+          <t>46,35%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>82,68%</t>
+          <t>82,78%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -12143,12 +12143,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>1306052</t>
+          <t>1307332</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>1349341</t>
+          <t>1350804</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -12158,12 +12158,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>89,36%</t>
+          <t>89,45%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>92,33%</t>
+          <t>92,43%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -12173,17 +12173,17 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>2731041</t>
+          <t>2731042</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>2121386</t>
+          <t>2155548</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>2959544</t>
+          <t>2956413</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -12193,12 +12193,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>62,13%</t>
+          <t>63,13%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>86,68%</t>
+          <t>86,59%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P64E-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P64E-Estudios-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1005</t>
+          <t>1010</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>8264</t>
+          <t>8294</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -753,7 +753,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>2,21%</t>
+          <t>2,22%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -773,7 +773,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>4848</t>
+          <t>5014</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>3,23%</t>
+          <t>3,34%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1036</t>
+          <t>1033</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>9225</t>
+          <t>11156</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -823,7 +823,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,76%</t>
+          <t>2,13%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>816</t>
+          <t>814</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>7513</t>
+          <t>8016</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -866,7 +866,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>2,01%</t>
+          <t>2,15%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -921,7 +921,7 @@
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>8439</t>
+          <t>7867</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -936,7 +936,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>1,5%</t>
         </is>
       </c>
     </row>
@@ -959,12 +959,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>1923</t>
+          <t>1958</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>10765</t>
+          <t>11501</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -974,12 +974,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>0,52%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>2,88%</t>
+          <t>3,08%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -1029,12 +1029,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>1915</t>
+          <t>1834</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>10941</t>
+          <t>11697</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>0,37%</t>
+          <t>0,35%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>2,09%</t>
+          <t>2,23%</t>
         </is>
       </c>
     </row>
@@ -1072,12 +1072,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>35221</t>
+          <t>33995</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>61270</t>
+          <t>60064</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1087,12 +1087,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>9,43%</t>
+          <t>9,1%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>16,4%</t>
+          <t>16,08%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>905</t>
+          <t>930</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>7909</t>
+          <t>8595</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1122,12 +1122,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>5,26%</t>
+          <t>5,72%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1142,12 +1142,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>38365</t>
+          <t>38219</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>66445</t>
+          <t>65131</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>7,32%</t>
+          <t>7,3%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>12,69%</t>
+          <t>12,43%</t>
         </is>
       </c>
     </row>
@@ -1185,12 +1185,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>300341</t>
+          <t>301035</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>328609</t>
+          <t>328944</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1200,12 +1200,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>80,41%</t>
+          <t>80,59%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>87,97%</t>
+          <t>88,06%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1220,12 +1220,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>141109</t>
+          <t>140122</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>149303</t>
+          <t>149278</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1235,12 +1235,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>93,9%</t>
+          <t>93,24%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,35%</t>
+          <t>99,34%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1255,12 +1255,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>443831</t>
+          <t>444868</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>475576</t>
+          <t>474295</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1270,12 +1270,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>84,73%</t>
+          <t>84,93%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>90,79%</t>
+          <t>90,55%</t>
         </is>
       </c>
     </row>
@@ -1415,12 +1415,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>8491</t>
+          <t>8141</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>26096</t>
+          <t>24213</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1430,12 +1430,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2,34%</t>
+          <t>2,18%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1455,7 +1455,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>6883</t>
+          <t>6866</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1485,12 +1485,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>9798</t>
+          <t>9374</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>28069</t>
+          <t>26039</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1500,12 +1500,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>0,55%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>1,54%</t>
         </is>
       </c>
     </row>
@@ -1528,12 +1528,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>9017</t>
+          <t>8966</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>25275</t>
+          <t>26361</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1548,7 +1548,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>2,27%</t>
+          <t>2,37%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1563,12 +1563,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>3655</t>
+          <t>3301</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>16004</t>
+          <t>16626</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1578,12 +1578,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,57%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>2,77%</t>
+          <t>2,88%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1598,12 +1598,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>14703</t>
+          <t>14067</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>35748</t>
+          <t>35272</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1613,12 +1613,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>0,83%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>2,11%</t>
+          <t>2,09%</t>
         </is>
       </c>
     </row>
@@ -1641,12 +1641,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>21249</t>
+          <t>21187</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>43992</t>
+          <t>41853</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1656,12 +1656,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>1,91%</t>
+          <t>1,9%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>3,95%</t>
+          <t>3,76%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1676,12 +1676,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>1053</t>
+          <t>1069</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>9737</t>
+          <t>10092</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1696,7 +1696,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>1,69%</t>
+          <t>1,75%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1711,12 +1711,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>25016</t>
+          <t>23872</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>48482</t>
+          <t>46152</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1726,12 +1726,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>1,41%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>2,87%</t>
+          <t>2,73%</t>
         </is>
       </c>
     </row>
@@ -1754,12 +1754,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>135307</t>
+          <t>131652</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>179899</t>
+          <t>179458</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1769,12 +1769,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>12,16%</t>
+          <t>11,83%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>16,16%</t>
+          <t>16,13%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1789,12 +1789,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>32610</t>
+          <t>32842</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>60091</t>
+          <t>60513</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>5,64%</t>
+          <t>5,68%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>10,4%</t>
+          <t>10,47%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1824,12 +1824,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>175631</t>
+          <t>174743</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>228537</t>
+          <t>225618</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1839,12 +1839,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>10,39%</t>
+          <t>10,34%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>13,52%</t>
+          <t>13,34%</t>
         </is>
       </c>
     </row>
@@ -1867,12 +1867,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>869955</t>
+          <t>869915</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>922273</t>
+          <t>923977</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1887,7 +1887,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>82,87%</t>
+          <t>83,02%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1902,12 +1902,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>500816</t>
+          <t>502465</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>532371</t>
+          <t>532529</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1917,12 +1917,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>86,68%</t>
+          <t>86,96%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>92,14%</t>
+          <t>92,17%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1937,12 +1937,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1382669</t>
+          <t>1384676</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1445043</t>
+          <t>1444126</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1952,12 +1952,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>81,78%</t>
+          <t>81,9%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>85,47%</t>
+          <t>85,42%</t>
         </is>
       </c>
     </row>
@@ -2097,12 +2097,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>7139</t>
+          <t>7300</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>21752</t>
+          <t>22864</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2112,12 +2112,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,79%</t>
+          <t>1,83%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>5,46%</t>
+          <t>5,73%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2132,12 +2132,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>2840</t>
+          <t>2894</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>13150</t>
+          <t>13434</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2147,12 +2147,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>4,54%</t>
+          <t>4,64%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2167,12 +2167,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>11844</t>
+          <t>12507</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>29939</t>
+          <t>30100</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2182,12 +2182,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,72%</t>
+          <t>1,82%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>4,35%</t>
+          <t>4,37%</t>
         </is>
       </c>
     </row>
@@ -2210,12 +2210,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>10555</t>
+          <t>10445</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>28975</t>
+          <t>27600</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2225,12 +2225,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>2,65%</t>
+          <t>2,62%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>7,27%</t>
+          <t>6,92%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2245,12 +2245,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3925</t>
+          <t>3945</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>15793</t>
+          <t>15392</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2265,7 +2265,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>5,46%</t>
+          <t>5,32%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2280,12 +2280,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>17173</t>
+          <t>17545</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>37106</t>
+          <t>38694</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2295,12 +2295,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>2,55%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>5,39%</t>
+          <t>5,62%</t>
         </is>
       </c>
     </row>
@@ -2323,12 +2323,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>8382</t>
+          <t>8195</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>24174</t>
+          <t>24331</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2338,12 +2338,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>2,06%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>6,06%</t>
+          <t>6,1%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2358,12 +2358,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>2012</t>
+          <t>2021</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>11802</t>
+          <t>11886</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2378,7 +2378,7 @@
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>4,08%</t>
+          <t>4,11%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2393,12 +2393,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>13149</t>
+          <t>12827</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>32195</t>
+          <t>32369</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2408,12 +2408,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>1,91%</t>
+          <t>1,86%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>4,68%</t>
+          <t>4,7%</t>
         </is>
       </c>
     </row>
@@ -2436,12 +2436,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>65363</t>
+          <t>66069</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>98307</t>
+          <t>97935</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2451,12 +2451,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>16,39%</t>
+          <t>16,57%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>24,66%</t>
+          <t>24,56%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2471,12 +2471,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>21440</t>
+          <t>21562</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>42434</t>
+          <t>44295</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2486,12 +2486,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>7,41%</t>
+          <t>7,45%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>14,66%</t>
+          <t>15,3%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2506,12 +2506,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>92614</t>
+          <t>93026</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>132232</t>
+          <t>132007</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2521,12 +2521,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>13,46%</t>
+          <t>13,52%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>19,21%</t>
+          <t>19,18%</t>
         </is>
       </c>
     </row>
@@ -2549,12 +2549,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>253700</t>
+          <t>251379</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>290269</t>
+          <t>289858</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2564,12 +2564,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>63,63%</t>
+          <t>63,05%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>72,8%</t>
+          <t>72,7%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2584,12 +2584,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>224679</t>
+          <t>223487</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>251137</t>
+          <t>250305</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2599,12 +2599,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>77,62%</t>
+          <t>77,2%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>86,75%</t>
+          <t>86,47%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2619,12 +2619,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>486057</t>
+          <t>486911</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>533533</t>
+          <t>532923</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2634,12 +2634,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>70,63%</t>
+          <t>70,75%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>77,53%</t>
+          <t>77,44%</t>
         </is>
       </c>
     </row>
@@ -2779,12 +2779,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>21475</t>
+          <t>20439</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>44181</t>
+          <t>43583</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2794,12 +2794,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>1,14%</t>
+          <t>1,08%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>2,34%</t>
+          <t>2,31%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2814,12 +2814,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>4769</t>
+          <t>4858</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>16554</t>
+          <t>16883</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2829,12 +2829,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>0,47%</t>
+          <t>0,48%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>1,63%</t>
+          <t>1,66%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2849,12 +2849,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>27229</t>
+          <t>29413</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>54350</t>
+          <t>56346</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2864,12 +2864,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>1,01%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>1,87%</t>
+          <t>1,94%</t>
         </is>
       </c>
     </row>
@@ -2892,12 +2892,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>24859</t>
+          <t>25610</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>49936</t>
+          <t>50431</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2907,82 +2907,82 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
+          <t>1,36%</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>2,68%</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="K23" s="2" t="inlineStr">
+        <is>
+          <t>16457</t>
+        </is>
+      </c>
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>9577</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>28658</t>
+        </is>
+      </c>
+      <c r="N23" s="2" t="inlineStr">
+        <is>
+          <t>1,62%</t>
+        </is>
+      </c>
+      <c r="O23" s="2" t="inlineStr">
+        <is>
+          <t>0,94%</t>
+        </is>
+      </c>
+      <c r="P23" s="2" t="inlineStr">
+        <is>
+          <t>2,82%</t>
+        </is>
+      </c>
+      <c r="Q23" s="2" t="inlineStr">
+        <is>
+          <t>48</t>
+        </is>
+      </c>
+      <c r="R23" s="2" t="inlineStr">
+        <is>
+          <t>52097</t>
+        </is>
+      </c>
+      <c r="S23" s="2" t="inlineStr">
+        <is>
+          <t>38206</t>
+        </is>
+      </c>
+      <c r="T23" s="2" t="inlineStr">
+        <is>
+          <t>68542</t>
+        </is>
+      </c>
+      <c r="U23" s="2" t="inlineStr">
+        <is>
+          <t>1,79%</t>
+        </is>
+      </c>
+      <c r="V23" s="2" t="inlineStr">
+        <is>
           <t>1,32%</t>
         </is>
       </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>2,65%</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="K23" s="2" t="inlineStr">
-        <is>
-          <t>16457</t>
-        </is>
-      </c>
-      <c r="L23" s="2" t="inlineStr">
-        <is>
-          <t>9543</t>
-        </is>
-      </c>
-      <c r="M23" s="2" t="inlineStr">
-        <is>
-          <t>26524</t>
-        </is>
-      </c>
-      <c r="N23" s="2" t="inlineStr">
-        <is>
-          <t>1,62%</t>
-        </is>
-      </c>
-      <c r="O23" s="2" t="inlineStr">
-        <is>
-          <t>0,94%</t>
-        </is>
-      </c>
-      <c r="P23" s="2" t="inlineStr">
-        <is>
-          <t>2,61%</t>
-        </is>
-      </c>
-      <c r="Q23" s="2" t="inlineStr">
-        <is>
-          <t>48</t>
-        </is>
-      </c>
-      <c r="R23" s="2" t="inlineStr">
-        <is>
-          <t>52097</t>
-        </is>
-      </c>
-      <c r="S23" s="2" t="inlineStr">
-        <is>
-          <t>38716</t>
-        </is>
-      </c>
-      <c r="T23" s="2" t="inlineStr">
-        <is>
-          <t>68742</t>
-        </is>
-      </c>
-      <c r="U23" s="2" t="inlineStr">
-        <is>
-          <t>1,79%</t>
-        </is>
-      </c>
-      <c r="V23" s="2" t="inlineStr">
-        <is>
-          <t>1,33%</t>
-        </is>
-      </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>2,37%</t>
+          <t>2,36%</t>
         </is>
       </c>
     </row>
@@ -3005,12 +3005,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>38088</t>
+          <t>38231</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>66490</t>
+          <t>67392</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3020,12 +3020,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>2,02%</t>
+          <t>2,03%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>3,53%</t>
+          <t>3,57%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3040,12 +3040,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>4951</t>
+          <t>4926</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>18738</t>
+          <t>16806</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3055,12 +3055,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>0,49%</t>
+          <t>0,48%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>1,84%</t>
+          <t>1,65%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3075,12 +3075,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>46098</t>
+          <t>46875</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>75946</t>
+          <t>77072</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3090,12 +3090,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>1,61%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>2,62%</t>
+          <t>2,66%</t>
         </is>
       </c>
     </row>
@@ -3118,12 +3118,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>254550</t>
+          <t>252096</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>313236</t>
+          <t>313693</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3133,12 +3133,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>13,5%</t>
+          <t>13,37%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>16,62%</t>
+          <t>16,64%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3153,12 +3153,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>63185</t>
+          <t>63985</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>99190</t>
+          <t>98230</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3168,12 +3168,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>6,21%</t>
+          <t>6,29%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>9,75%</t>
+          <t>9,65%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3188,12 +3188,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>327103</t>
+          <t>326125</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>400040</t>
+          <t>395612</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3203,12 +3203,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>11,27%</t>
+          <t>11,24%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>13,78%</t>
+          <t>13,63%</t>
         </is>
       </c>
     </row>
@@ -3231,12 +3231,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>1448314</t>
+          <t>1449391</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>1521671</t>
+          <t>1518683</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3246,12 +3246,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>76,83%</t>
+          <t>76,88%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>80,72%</t>
+          <t>80,56%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3266,12 +3266,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>879254</t>
+          <t>879880</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>922111</t>
+          <t>922157</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3281,12 +3281,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>86,41%</t>
+          <t>86,47%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>90,62%</t>
+          <t>90,63%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3301,12 +3301,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>2346319</t>
+          <t>2348372</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>2427134</t>
+          <t>2429141</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3316,12 +3316,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>80,83%</t>
+          <t>80,9%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>83,62%</t>
+          <t>83,69%</t>
         </is>
       </c>
     </row>
@@ -3697,7 +3697,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>6856</t>
+          <t>5923</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3712,7 +3712,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>3,73%</t>
+          <t>3,22%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3767,7 +3767,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>6881</t>
+          <t>6438</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3782,7 +3782,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,12%</t>
+          <t>1,99%</t>
         </is>
       </c>
     </row>
@@ -3810,7 +3810,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>4961</t>
+          <t>6523</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3825,7 +3825,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>3,54%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3880,7 +3880,7 @@
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>5419</t>
+          <t>6072</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3895,7 +3895,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>1,87%</t>
         </is>
       </c>
     </row>
@@ -3923,7 +3923,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>5788</t>
+          <t>6564</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -3938,7 +3938,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>3,15%</t>
+          <t>3,57%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -3958,7 +3958,7 @@
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>7114</t>
+          <t>6204</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3973,7 +3973,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>5,08%</t>
+          <t>4,43%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -3988,12 +3988,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>1031</t>
+          <t>1016</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>9537</t>
+          <t>9776</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4003,12 +4003,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>0,32%</t>
+          <t>0,31%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>2,94%</t>
+          <t>3,02%</t>
         </is>
       </c>
     </row>
@@ -4031,12 +4031,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>13372</t>
+          <t>13041</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>31213</t>
+          <t>29990</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4046,12 +4046,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>7,27%</t>
+          <t>7,09%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>16,96%</t>
+          <t>16,3%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4066,12 +4066,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>5241</t>
+          <t>5313</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>20205</t>
+          <t>20392</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4081,12 +4081,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>3,74%</t>
+          <t>3,8%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>14,43%</t>
+          <t>14,57%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4101,12 +4101,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>21322</t>
+          <t>22581</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>43512</t>
+          <t>45206</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4116,12 +4116,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>6,58%</t>
+          <t>6,97%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>13,43%</t>
+          <t>13,95%</t>
         </is>
       </c>
     </row>
@@ -4144,12 +4144,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>147682</t>
+          <t>147689</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>166681</t>
+          <t>166331</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4159,12 +4159,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>80,25%</t>
+          <t>80,26%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>90,58%</t>
+          <t>90,39%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4179,12 +4179,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>117334</t>
+          <t>118173</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>132962</t>
+          <t>132988</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4194,12 +4194,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>83,82%</t>
+          <t>84,42%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>94,99%</t>
+          <t>95,01%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4214,12 +4214,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>273537</t>
+          <t>271016</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>296325</t>
+          <t>295761</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4229,12 +4229,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>84,43%</t>
+          <t>83,65%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>91,46%</t>
+          <t>91,29%</t>
         </is>
       </c>
     </row>
@@ -4374,12 +4374,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>8038</t>
+          <t>8711</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>26234</t>
+          <t>26874</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4389,12 +4389,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>0,95%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2,87%</t>
+          <t>2,94%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4414,7 +4414,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>6798</t>
+          <t>6893</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4429,42 +4429,42 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
+          <t>1,21%</t>
+        </is>
+      </c>
+      <c r="Q10" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="R10" s="2" t="inlineStr">
+        <is>
+          <t>17706</t>
+        </is>
+      </c>
+      <c r="S10" s="2" t="inlineStr">
+        <is>
+          <t>10451</t>
+        </is>
+      </c>
+      <c r="T10" s="2" t="inlineStr">
+        <is>
+          <t>30943</t>
+        </is>
+      </c>
+      <c r="U10" s="2" t="inlineStr">
+        <is>
           <t>1,19%</t>
         </is>
       </c>
-      <c r="Q10" s="2" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="R10" s="2" t="inlineStr">
-        <is>
-          <t>17706</t>
-        </is>
-      </c>
-      <c r="S10" s="2" t="inlineStr">
-        <is>
-          <t>10023</t>
-        </is>
-      </c>
-      <c r="T10" s="2" t="inlineStr">
-        <is>
-          <t>29833</t>
-        </is>
-      </c>
-      <c r="U10" s="2" t="inlineStr">
-        <is>
-          <t>1,19%</t>
-        </is>
-      </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,01%</t>
+          <t>2,08%</t>
         </is>
       </c>
     </row>
@@ -4487,12 +4487,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>5641</t>
+          <t>5670</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>21271</t>
+          <t>21568</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4507,7 +4507,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>2,33%</t>
+          <t>2,36%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4522,12 +4522,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>2868</t>
+          <t>2156</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>14825</t>
+          <t>15055</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4537,12 +4537,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,38%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>2,59%</t>
+          <t>2,63%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4557,12 +4557,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>10276</t>
+          <t>10757</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>30107</t>
+          <t>29739</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4572,12 +4572,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,72%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>2,03%</t>
+          <t>2,0%</t>
         </is>
       </c>
     </row>
@@ -4600,12 +4600,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>14624</t>
+          <t>14357</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>33330</t>
+          <t>33825</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -4615,12 +4615,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>1,57%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>3,65%</t>
+          <t>3,71%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -4635,12 +4635,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>3067</t>
+          <t>3105</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>15674</t>
+          <t>15722</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -4655,7 +4655,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>2,74%</t>
+          <t>2,75%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -4670,12 +4670,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>21517</t>
+          <t>21202</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>45580</t>
+          <t>44572</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -4685,12 +4685,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>1,45%</t>
+          <t>1,43%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>3,07%</t>
+          <t>3,0%</t>
         </is>
       </c>
     </row>
@@ -4713,12 +4713,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>135197</t>
+          <t>133763</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>181448</t>
+          <t>184528</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4728,12 +4728,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>14,82%</t>
+          <t>14,66%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>19,88%</t>
+          <t>20,22%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4748,12 +4748,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>36122</t>
+          <t>36184</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>63871</t>
+          <t>63985</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4763,12 +4763,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>6,32%</t>
+          <t>6,33%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>11,17%</t>
+          <t>11,19%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4783,12 +4783,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>177062</t>
+          <t>177515</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>230998</t>
+          <t>232226</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>11,93%</t>
+          <t>11,96%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>15,56%</t>
+          <t>15,64%</t>
         </is>
       </c>
     </row>
@@ -4826,12 +4826,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>677410</t>
+          <t>676405</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>729433</t>
+          <t>729897</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4841,12 +4841,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>74,23%</t>
+          <t>74,12%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>79,93%</t>
+          <t>79,99%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4861,12 +4861,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>490155</t>
+          <t>489861</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>521338</t>
+          <t>522445</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4876,12 +4876,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>85,7%</t>
+          <t>85,65%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>91,15%</t>
+          <t>91,35%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4896,12 +4896,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1183447</t>
+          <t>1179027</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1246277</t>
+          <t>1241528</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4911,12 +4911,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>79,72%</t>
+          <t>79,42%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>83,95%</t>
+          <t>83,63%</t>
         </is>
       </c>
     </row>
@@ -5056,12 +5056,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>6103</t>
+          <t>5419</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>25559</t>
+          <t>23537</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5071,12 +5071,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,94%</t>
+          <t>1,72%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>8,11%</t>
+          <t>7,46%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5091,12 +5091,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>938</t>
+          <t>927</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>8192</t>
+          <t>8984</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5106,12 +5106,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,39%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>3,49%</t>
+          <t>3,82%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5126,12 +5126,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>7125</t>
+          <t>7966</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>25358</t>
+          <t>27692</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5141,12 +5141,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>1,45%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>4,61%</t>
+          <t>5,03%</t>
         </is>
       </c>
     </row>
@@ -5169,12 +5169,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>6540</t>
+          <t>5704</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>21148</t>
+          <t>19759</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5184,12 +5184,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>2,07%</t>
+          <t>1,81%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>6,71%</t>
+          <t>6,27%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5204,12 +5204,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>984</t>
+          <t>987</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>8374</t>
+          <t>7760</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5224,7 +5224,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>3,57%</t>
+          <t>3,3%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5239,12 +5239,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>8208</t>
+          <t>8671</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>23979</t>
+          <t>24935</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5254,12 +5254,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>1,49%</t>
+          <t>1,58%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>4,36%</t>
+          <t>4,53%</t>
         </is>
       </c>
     </row>
@@ -5282,12 +5282,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>8199</t>
+          <t>7390</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>24626</t>
+          <t>23625</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -5297,12 +5297,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>2,34%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>7,81%</t>
+          <t>7,49%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -5322,7 +5322,7 @@
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>5439</t>
+          <t>5383</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -5337,7 +5337,7 @@
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>2,32%</t>
+          <t>2,29%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -5352,12 +5352,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>8379</t>
+          <t>8741</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>26150</t>
+          <t>26512</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -5367,12 +5367,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>1,52%</t>
+          <t>1,59%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>4,75%</t>
+          <t>4,82%</t>
         </is>
       </c>
     </row>
@@ -5395,12 +5395,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>68152</t>
+          <t>68432</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>100653</t>
+          <t>101048</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5410,12 +5410,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>21,61%</t>
+          <t>21,7%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>31,92%</t>
+          <t>32,05%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5430,12 +5430,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>19958</t>
+          <t>20283</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>43625</t>
+          <t>43808</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5445,12 +5445,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>8,5%</t>
+          <t>8,63%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>18,57%</t>
+          <t>18,65%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5465,12 +5465,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>94111</t>
+          <t>93579</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>136339</t>
+          <t>134873</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5480,12 +5480,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>17,1%</t>
+          <t>17,01%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>24,78%</t>
+          <t>24,51%</t>
         </is>
       </c>
     </row>
@@ -5508,12 +5508,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>176142</t>
+          <t>175381</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>212051</t>
+          <t>211630</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5523,12 +5523,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>55,86%</t>
+          <t>55,62%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>67,25%</t>
+          <t>67,12%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5543,12 +5543,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>182955</t>
+          <t>183268</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>209402</t>
+          <t>208489</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5558,12 +5558,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>77,89%</t>
+          <t>78,02%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>89,15%</t>
+          <t>88,76%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5578,12 +5578,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>367733</t>
+          <t>369519</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>415799</t>
+          <t>413567</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5593,12 +5593,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>66,83%</t>
+          <t>67,16%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>75,57%</t>
+          <t>75,16%</t>
         </is>
       </c>
     </row>
@@ -5738,12 +5738,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>19958</t>
+          <t>19875</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>45656</t>
+          <t>44567</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5758,7 +5758,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>3,23%</t>
+          <t>3,16%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5773,12 +5773,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>1948</t>
+          <t>1897</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>11831</t>
+          <t>10888</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5788,12 +5788,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>0,21%</t>
+          <t>0,2%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>1,15%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5808,12 +5808,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>23282</t>
+          <t>24380</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>49628</t>
+          <t>51447</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5823,12 +5823,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>1,03%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>2,18%</t>
         </is>
       </c>
     </row>
@@ -5851,12 +5851,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>15503</t>
+          <t>15578</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>35956</t>
+          <t>36535</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5871,7 +5871,7 @@
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>2,55%</t>
+          <t>2,59%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5886,12 +5886,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>5048</t>
+          <t>5019</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>18571</t>
+          <t>19597</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5906,7 +5906,7 @@
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>1,96%</t>
+          <t>2,07%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5921,12 +5921,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>23374</t>
+          <t>23696</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>47673</t>
+          <t>49477</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5936,12 +5936,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>2,02%</t>
+          <t>2,1%</t>
         </is>
       </c>
     </row>
@@ -5964,12 +5964,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>27856</t>
+          <t>27823</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>52956</t>
+          <t>52762</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -5984,7 +5984,7 @@
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>3,75%</t>
+          <t>3,74%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -5999,12 +5999,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>5770</t>
+          <t>5127</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>19045</t>
+          <t>20737</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -6014,12 +6014,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,54%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>2,01%</t>
+          <t>2,19%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -6034,12 +6034,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>36526</t>
+          <t>36602</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>65436</t>
+          <t>66084</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -6054,7 +6054,7 @@
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>2,77%</t>
+          <t>2,8%</t>
         </is>
       </c>
     </row>
@@ -6077,12 +6077,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>228786</t>
+          <t>231159</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>291393</t>
+          <t>289693</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6092,12 +6092,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>16,2%</t>
+          <t>16,37%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>20,64%</t>
+          <t>20,52%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6112,12 +6112,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>73081</t>
+          <t>71332</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>109883</t>
+          <t>110457</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6127,12 +6127,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>7,72%</t>
+          <t>7,53%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>11,61%</t>
+          <t>11,67%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6147,12 +6147,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>313431</t>
+          <t>316530</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>383995</t>
+          <t>385532</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6162,12 +6162,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>13,29%</t>
+          <t>13,42%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>16,28%</t>
+          <t>16,35%</t>
         </is>
       </c>
     </row>
@@ -6190,12 +6190,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>1023448</t>
+          <t>1026823</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>1092986</t>
+          <t>1091198</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6205,12 +6205,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>72,49%</t>
+          <t>72,73%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>77,41%</t>
+          <t>77,29%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6225,12 +6225,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>809602</t>
+          <t>806392</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>850409</t>
+          <t>851504</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6240,12 +6240,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>85,51%</t>
+          <t>85,17%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>89,82%</t>
+          <t>89,93%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6260,12 +6260,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1853411</t>
+          <t>1845595</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1931145</t>
+          <t>1926014</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6275,12 +6275,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>78,58%</t>
+          <t>78,25%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>81,87%</t>
+          <t>81,66%</t>
         </is>
       </c>
     </row>
@@ -6877,12 +6877,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>1945</t>
+          <t>1943</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>11421</t>
+          <t>11040</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -6897,7 +6897,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>8,16%</t>
+          <t>7,89%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -6917,7 +6917,7 @@
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>4639</t>
+          <t>5733</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6932,7 +6932,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>6,52%</t>
+          <t>8,06%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -6947,12 +6947,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>2081</t>
+          <t>2885</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>13393</t>
+          <t>13032</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6962,12 +6962,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>1,37%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>6,35%</t>
+          <t>6,17%</t>
         </is>
       </c>
     </row>
@@ -6990,12 +6990,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>11013</t>
+          <t>11440</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>27668</t>
+          <t>27769</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7005,12 +7005,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>7,87%</t>
+          <t>8,17%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>19,77%</t>
+          <t>19,84%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7025,12 +7025,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>874</t>
+          <t>883</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>8202</t>
+          <t>8363</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7040,12 +7040,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,23%</t>
+          <t>1,24%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>11,53%</t>
+          <t>11,76%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7060,12 +7060,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>13778</t>
+          <t>13811</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>31862</t>
+          <t>31522</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7075,12 +7075,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>6,53%</t>
+          <t>6,54%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>15,1%</t>
+          <t>14,93%</t>
         </is>
       </c>
     </row>
@@ -7103,12 +7103,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>107061</t>
+          <t>107384</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>124970</t>
+          <t>124176</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7118,12 +7118,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>76,49%</t>
+          <t>76,72%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>89,29%</t>
+          <t>88,72%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7138,12 +7138,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>61350</t>
+          <t>61762</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>70043</t>
+          <t>69984</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7153,12 +7153,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>86,28%</t>
+          <t>86,86%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>98,51%</t>
+          <t>98,43%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7173,12 +7173,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>172680</t>
+          <t>173077</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>191762</t>
+          <t>192314</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7188,12 +7188,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>81,81%</t>
+          <t>82,0%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>90,85%</t>
+          <t>91,11%</t>
         </is>
       </c>
     </row>
@@ -7333,12 +7333,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>2166</t>
+          <t>2965</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>14468</t>
+          <t>15344</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7348,12 +7348,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,24%</t>
+          <t>0,32%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>1,58%</t>
+          <t>1,67%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7368,12 +7368,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>1887</t>
+          <t>1886</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>12957</t>
+          <t>12928</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7403,12 +7403,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>6486</t>
+          <t>5934</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>20746</t>
+          <t>21357</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7418,12 +7418,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,38%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,36%</t>
         </is>
       </c>
     </row>
@@ -7446,12 +7446,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>5118</t>
+          <t>5357</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>19926</t>
+          <t>20961</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7461,12 +7461,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>0,58%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>2,17%</t>
+          <t>2,28%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7486,7 +7486,7 @@
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>5095</t>
+          <t>4843</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7501,7 +7501,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>0,75%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7516,12 +7516,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>5872</t>
+          <t>5587</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>20738</t>
+          <t>21769</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7531,12 +7531,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>0,37%</t>
+          <t>0,36%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,39%</t>
         </is>
       </c>
     </row>
@@ -7559,12 +7559,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>12628</t>
+          <t>11283</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>31561</t>
+          <t>30810</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -7574,12 +7574,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>1,23%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>3,44%</t>
+          <t>3,36%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -7594,12 +7594,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>3176</t>
+          <t>3725</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>15962</t>
+          <t>16279</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -7609,12 +7609,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>0,49%</t>
+          <t>0,57%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>2,46%</t>
+          <t>2,51%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -7629,12 +7629,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>18355</t>
+          <t>17994</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>41114</t>
+          <t>39915</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -7644,12 +7644,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,15%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>2,62%</t>
+          <t>2,55%</t>
         </is>
       </c>
     </row>
@@ -7672,12 +7672,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>80754</t>
+          <t>83693</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>120522</t>
+          <t>123159</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7687,12 +7687,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>8,8%</t>
+          <t>9,12%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>13,13%</t>
+          <t>13,41%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7707,12 +7707,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>30020</t>
+          <t>29852</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>55688</t>
+          <t>56528</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7722,12 +7722,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>4,62%</t>
+          <t>4,6%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>8,57%</t>
+          <t>8,7%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7742,12 +7742,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>121504</t>
+          <t>122488</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>167696</t>
+          <t>168611</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7757,12 +7757,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>7,75%</t>
+          <t>7,81%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>10,7%</t>
+          <t>10,76%</t>
         </is>
       </c>
     </row>
@@ -7785,12 +7785,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>754467</t>
+          <t>754903</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>801790</t>
+          <t>800774</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7800,12 +7800,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>82,18%</t>
+          <t>82,22%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>87,33%</t>
+          <t>87,22%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7820,12 +7820,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>578594</t>
+          <t>577954</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>606876</t>
+          <t>607344</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7835,12 +7835,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>89,07%</t>
+          <t>88,97%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>93,42%</t>
+          <t>93,5%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7855,12 +7855,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1346543</t>
+          <t>1343647</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1397164</t>
+          <t>1397939</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7870,12 +7870,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>85,89%</t>
+          <t>85,71%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>89,12%</t>
+          <t>89,17%</t>
         </is>
       </c>
     </row>
@@ -8015,12 +8015,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>5798</t>
+          <t>5541</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>20179</t>
+          <t>19987</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8030,12 +8030,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>1,59%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>5,8%</t>
+          <t>5,74%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8055,7 +8055,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>5985</t>
+          <t>5569</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8070,7 +8070,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>1,96%</t>
+          <t>1,82%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8085,12 +8085,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>6872</t>
+          <t>6639</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>22492</t>
+          <t>22479</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8100,7 +8100,7 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>1,02%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
@@ -8128,12 +8128,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3145</t>
+          <t>3220</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>15651</t>
+          <t>16490</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8143,12 +8143,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,93%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>4,5%</t>
+          <t>4,74%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8163,12 +8163,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>1855</t>
+          <t>1834</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>10398</t>
+          <t>10343</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8178,12 +8178,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>3,4%</t>
+          <t>3,38%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8198,12 +8198,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>6978</t>
+          <t>7000</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>22414</t>
+          <t>22119</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8218,7 +8218,7 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>3,43%</t>
+          <t>3,38%</t>
         </is>
       </c>
     </row>
@@ -8241,12 +8241,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>11422</t>
+          <t>11228</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>29979</t>
+          <t>29124</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -8256,12 +8256,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>3,28%</t>
+          <t>3,23%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>8,61%</t>
+          <t>8,37%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -8276,12 +8276,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>3526</t>
+          <t>3788</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>15508</t>
+          <t>15526</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -8291,12 +8291,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>1,24%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>5,07%</t>
+          <t>5,08%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -8311,12 +8311,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>16826</t>
+          <t>17010</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>38665</t>
+          <t>38829</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -8326,12 +8326,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>2,57%</t>
+          <t>2,6%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>5,92%</t>
+          <t>5,94%</t>
         </is>
       </c>
     </row>
@@ -8354,12 +8354,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>42528</t>
+          <t>44052</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>72700</t>
+          <t>74077</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -8369,12 +8369,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>12,22%</t>
+          <t>12,66%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>20,89%</t>
+          <t>21,28%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -8389,12 +8389,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>19108</t>
+          <t>20433</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>40834</t>
+          <t>41634</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -8404,12 +8404,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>6,25%</t>
+          <t>6,69%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>13,36%</t>
+          <t>13,62%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -8424,12 +8424,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>70081</t>
+          <t>70024</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>105832</t>
+          <t>106281</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -8439,12 +8439,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>10,72%</t>
+          <t>10,71%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>16,19%</t>
+          <t>16,26%</t>
         </is>
       </c>
     </row>
@@ -8467,12 +8467,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>234895</t>
+          <t>234109</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>270113</t>
+          <t>268826</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -8482,12 +8482,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>67,49%</t>
+          <t>67,26%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>77,61%</t>
+          <t>77,24%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -8502,12 +8502,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>247798</t>
+          <t>247551</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>273261</t>
+          <t>272676</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -8517,12 +8517,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>81,08%</t>
+          <t>81,0%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>89,42%</t>
+          <t>89,22%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -8537,12 +8537,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>492023</t>
+          <t>490487</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>535162</t>
+          <t>535182</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -8552,12 +8552,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>75,27%</t>
+          <t>75,04%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>81,87%</t>
+          <t>81,88%</t>
         </is>
       </c>
     </row>
@@ -8697,12 +8697,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>10689</t>
+          <t>11074</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>29006</t>
+          <t>30965</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8712,12 +8712,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>0,79%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>2,06%</t>
+          <t>2,2%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8732,12 +8732,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>3490</t>
+          <t>2878</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>14678</t>
+          <t>14411</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8747,12 +8747,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>0,34%</t>
+          <t>0,28%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>1,43%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8767,12 +8767,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>17067</t>
+          <t>16501</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>38958</t>
+          <t>39072</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8782,12 +8782,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,68%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>1,61%</t>
         </is>
       </c>
     </row>
@@ -8810,12 +8810,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>11111</t>
+          <t>10930</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>31537</t>
+          <t>30195</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8825,12 +8825,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>0,78%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>2,24%</t>
+          <t>2,15%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8845,12 +8845,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>1894</t>
+          <t>1905</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>11998</t>
+          <t>12207</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8860,12 +8860,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>0,18%</t>
+          <t>0,19%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,19%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8880,12 +8880,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>15709</t>
+          <t>15767</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>36321</t>
+          <t>38060</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8900,7 +8900,7 @@
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>1,49%</t>
+          <t>1,56%</t>
         </is>
       </c>
     </row>
@@ -8923,12 +8923,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>31368</t>
+          <t>32063</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>59422</t>
+          <t>58113</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -8938,12 +8938,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>2,23%</t>
+          <t>2,28%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>4,23%</t>
+          <t>4,13%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -8958,12 +8958,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>10087</t>
+          <t>10612</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>26709</t>
+          <t>27788</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -8973,12 +8973,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>1,03%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>2,71%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -8993,12 +8993,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>45804</t>
+          <t>45472</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>79677</t>
+          <t>76778</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -9008,12 +9008,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>1,88%</t>
+          <t>1,87%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>3,28%</t>
+          <t>3,16%</t>
         </is>
       </c>
     </row>
@@ -9036,12 +9036,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>150671</t>
+          <t>149165</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>203912</t>
+          <t>203334</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9051,12 +9051,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>10,72%</t>
+          <t>10,61%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>14,5%</t>
+          <t>14,46%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9071,12 +9071,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>58290</t>
+          <t>58842</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>92090</t>
+          <t>92038</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9086,7 +9086,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>5,68%</t>
+          <t>5,73%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -9106,12 +9106,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>222615</t>
+          <t>219098</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>283539</t>
+          <t>281396</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9121,12 +9121,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>9,15%</t>
+          <t>9,01%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>11,66%</t>
+          <t>11,57%</t>
         </is>
       </c>
     </row>
@@ -9149,12 +9149,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>1119010</t>
+          <t>1118920</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>1179113</t>
+          <t>1178182</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9164,12 +9164,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>79,58%</t>
+          <t>79,57%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>83,86%</t>
+          <t>83,79%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9184,12 +9184,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>901864</t>
+          <t>900844</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>940101</t>
+          <t>939573</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9199,12 +9199,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>87,88%</t>
+          <t>87,78%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>91,6%</t>
+          <t>91,55%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9219,12 +9219,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>2028049</t>
+          <t>2033396</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>2102251</t>
+          <t>2107248</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9234,12 +9234,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>83,38%</t>
+          <t>83,6%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>86,43%</t>
+          <t>86,63%</t>
         </is>
       </c>
     </row>
@@ -9718,32 +9718,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>5954</t>
+          <t>5597</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1985</t>
+          <t>2032</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>13261</t>
+          <t>12567</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>4,51%</t>
+          <t>3,41%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>1,24%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>10,04%</t>
+          <t>7,67%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -9788,32 +9788,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>5954</t>
+          <t>5597</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1958</t>
+          <t>2153</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>13708</t>
+          <t>12282</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>2,77%</t>
+          <t>2,21%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>0,85%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>6,37%</t>
+          <t>4,85%</t>
         </is>
       </c>
     </row>
@@ -9831,7 +9831,7 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>1401</t>
+          <t>1387</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -9841,12 +9841,12 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>5401</t>
+          <t>4828</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>0,85%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
@@ -9856,7 +9856,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>4,09%</t>
+          <t>2,94%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -9901,7 +9901,7 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>1401</t>
+          <t>1387</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
@@ -9911,12 +9911,12 @@
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>5110</t>
+          <t>4719</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>0,55%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
@@ -9926,7 +9926,7 @@
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>2,38%</t>
+          <t>1,86%</t>
         </is>
       </c>
     </row>
@@ -9944,32 +9944,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>5960</t>
+          <t>7194</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2109</t>
+          <t>2912</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>15667</t>
+          <t>17146</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>4,51%</t>
+          <t>4,39%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>1,78%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>11,86%</t>
+          <t>10,46%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -9979,32 +9979,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>5709</t>
+          <t>5853</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>2582</t>
+          <t>2687</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>10616</t>
+          <t>10811</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>6,88%</t>
+          <t>6,55%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>3,11%</t>
+          <t>3,01%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>12,8%</t>
+          <t>12,1%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -10014,32 +10014,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>11670</t>
+          <t>13048</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>6429</t>
+          <t>7064</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>20560</t>
+          <t>22940</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>5,43%</t>
+          <t>5,15%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,99%</t>
+          <t>2,79%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>9,56%</t>
+          <t>9,06%</t>
         </is>
       </c>
     </row>
@@ -10057,32 +10057,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>118787</t>
+          <t>149757</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>109166</t>
+          <t>140130</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>124446</t>
+          <t>156342</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>89,92%</t>
+          <t>91,35%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>82,64%</t>
+          <t>85,48%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>94,2%</t>
+          <t>95,37%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -10092,32 +10092,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>77240</t>
+          <t>83470</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>72333</t>
+          <t>78512</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>80367</t>
+          <t>86636</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>93,12%</t>
+          <t>93,45%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>87,2%</t>
+          <t>87,9%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>96,89%</t>
+          <t>96,99%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -10127,32 +10127,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>196027</t>
+          <t>233226</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>185448</t>
+          <t>222643</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>203205</t>
+          <t>240890</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>91,15%</t>
+          <t>92,09%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>86,23%</t>
+          <t>87,91%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>94,49%</t>
+          <t>95,12%</t>
         </is>
       </c>
     </row>
@@ -10170,17 +10170,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>132103</t>
+          <t>163935</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>132103</t>
+          <t>163935</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>132103</t>
+          <t>163935</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -10205,17 +10205,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>82949</t>
+          <t>89323</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>82949</t>
+          <t>89323</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>82949</t>
+          <t>89323</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -10240,17 +10240,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>215052</t>
+          <t>253258</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>215052</t>
+          <t>253258</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>215052</t>
+          <t>253258</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -10287,32 +10287,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>19636</t>
+          <t>20028</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>9094</t>
+          <t>12081</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>31378</t>
+          <t>31262</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>1,43%</t>
+          <t>1,58%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>0,96%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2,28%</t>
+          <t>2,47%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -10322,32 +10322,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>2077</t>
+          <t>2691</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>602</t>
+          <t>942</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>5754</t>
+          <t>7627</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>0,22%</t>
+          <t>0,29%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,06%</t>
+          <t>0,1%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,81%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -10357,32 +10357,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>21713</t>
+          <t>22719</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>12625</t>
+          <t>15095</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>33727</t>
+          <t>35805</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>1,03%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,54%</t>
+          <t>0,68%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,45%</t>
+          <t>1,62%</t>
         </is>
       </c>
     </row>
@@ -10400,32 +10400,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>257234</t>
+          <t>13955</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>11866</t>
+          <t>7692</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>724200</t>
+          <t>22655</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>18,68%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>0,61%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>52,6%</t>
+          <t>1,79%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -10435,32 +10435,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>5945</t>
+          <t>6259</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>2692</t>
+          <t>2546</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>11749</t>
+          <t>11911</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,66%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>0,29%</t>
+          <t>0,27%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>1,26%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -10470,32 +10470,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>263179</t>
+          <t>20214</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>17590</t>
+          <t>12947</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>786734</t>
+          <t>30701</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>11,34%</t>
+          <t>0,92%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>0,59%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>33,91%</t>
+          <t>1,39%</t>
         </is>
       </c>
     </row>
@@ -10513,32 +10513,32 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>35000</t>
+          <t>37735</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>17931</t>
+          <t>26486</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>52554</t>
+          <t>59087</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>2,54%</t>
+          <t>2,98%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>2,09%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>3,82%</t>
+          <t>4,67%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -10548,32 +10548,32 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>9351</t>
+          <t>10492</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>4894</t>
+          <t>5802</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>16245</t>
+          <t>17087</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>1,11%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>0,61%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>1,72%</t>
+          <t>1,81%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -10583,32 +10583,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>44352</t>
+          <t>48227</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>27657</t>
+          <t>34931</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>62946</t>
+          <t>66094</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>1,91%</t>
+          <t>2,18%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,58%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>2,71%</t>
+          <t>2,99%</t>
         </is>
       </c>
     </row>
@@ -10626,32 +10626,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>104901</t>
+          <t>117533</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>58369</t>
+          <t>95954</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>135290</t>
+          <t>140292</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>7,62%</t>
+          <t>9,3%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>4,24%</t>
+          <t>7,59%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>9,83%</t>
+          <t>11,1%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -10661,32 +10661,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>41960</t>
+          <t>48945</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>30899</t>
+          <t>38509</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>54770</t>
+          <t>62154</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>4,45%</t>
+          <t>5,19%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>3,28%</t>
+          <t>4,08%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>5,81%</t>
+          <t>6,59%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -10696,32 +10696,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>146861</t>
+          <t>166478</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>103987</t>
+          <t>141739</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>175998</t>
+          <t>193872</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>6,33%</t>
+          <t>7,54%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>4,48%</t>
+          <t>6,42%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>7,59%</t>
+          <t>8,78%</t>
         </is>
       </c>
     </row>
@@ -10739,32 +10739,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>960146</t>
+          <t>1075145</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>558977</t>
+          <t>1048546</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1176509</t>
+          <t>1104972</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>69,73%</t>
+          <t>85,03%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>40,6%</t>
+          <t>82,93%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>85,45%</t>
+          <t>87,39%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -10774,32 +10774,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>883979</t>
+          <t>875300</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>867516</t>
+          <t>860042</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>898647</t>
+          <t>887558</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>93,71%</t>
+          <t>92,75%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>91,96%</t>
+          <t>91,14%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>95,27%</t>
+          <t>94,05%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -10809,32 +10809,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>1844125</t>
+          <t>1950445</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1366730</t>
+          <t>1918574</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>2073506</t>
+          <t>1980942</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>79,48%</t>
+          <t>88,33%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>58,9%</t>
+          <t>86,89%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>89,37%</t>
+          <t>89,71%</t>
         </is>
       </c>
     </row>
@@ -10852,17 +10852,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1376918</t>
+          <t>1264395</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1376918</t>
+          <t>1264395</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>1376918</t>
+          <t>1264395</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -10887,17 +10887,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>943312</t>
+          <t>943688</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>943312</t>
+          <t>943688</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>943312</t>
+          <t>943688</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -10922,17 +10922,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>2320230</t>
+          <t>2208083</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>2320230</t>
+          <t>2208083</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>2320230</t>
+          <t>2208083</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -10969,22 +10969,22 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>20440</t>
+          <t>21363</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>12397</t>
+          <t>13477</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>30359</t>
+          <t>33399</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>4,61%</t>
+          <t>4,42%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
@@ -10994,7 +10994,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>6,84%</t>
+          <t>6,9%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -11004,32 +11004,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>6687</t>
+          <t>7316</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>3167</t>
+          <t>3442</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>12135</t>
+          <t>12361</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>1,54%</t>
+          <t>1,53%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,72%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>2,79%</t>
+          <t>2,58%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -11039,32 +11039,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>27126</t>
+          <t>28679</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>17976</t>
+          <t>19766</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>37604</t>
+          <t>40482</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>3,09%</t>
+          <t>2,98%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>2,04%</t>
+          <t>2,05%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>4,28%</t>
+          <t>4,21%</t>
         </is>
       </c>
     </row>
@@ -11082,32 +11082,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>10839</t>
+          <t>11308</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>5587</t>
+          <t>5799</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>19899</t>
+          <t>21045</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>2,44%</t>
+          <t>2,34%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>4,48%</t>
+          <t>4,35%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -11117,32 +11117,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>10148</t>
+          <t>11982</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>5872</t>
+          <t>7074</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>16337</t>
+          <t>19387</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>2,33%</t>
+          <t>2,51%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>1,35%</t>
+          <t>1,48%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>3,75%</t>
+          <t>4,05%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -11152,32 +11152,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>20987</t>
+          <t>23290</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>13389</t>
+          <t>15666</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>31149</t>
+          <t>34248</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>2,39%</t>
+          <t>2,42%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>1,52%</t>
+          <t>1,63%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>3,54%</t>
+          <t>3,56%</t>
         </is>
       </c>
     </row>
@@ -11195,32 +11195,32 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>22234</t>
+          <t>24134</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>14868</t>
+          <t>15788</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>32673</t>
+          <t>35661</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>5,01%</t>
+          <t>4,99%</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>3,35%</t>
+          <t>3,26%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>7,36%</t>
+          <t>7,37%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -11230,32 +11230,32 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>10580</t>
+          <t>10811</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>6123</t>
+          <t>6478</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>16579</t>
+          <t>17262</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>2,43%</t>
+          <t>2,26%</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>1,35%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>3,81%</t>
+          <t>3,61%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -11265,32 +11265,32 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>32814</t>
+          <t>34945</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>24072</t>
+          <t>24467</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>45177</t>
+          <t>48099</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>3,73%</t>
+          <t>3,63%</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>2,74%</t>
+          <t>2,54%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>5,14%</t>
+          <t>5,0%</t>
         </is>
       </c>
     </row>
@@ -11308,32 +11308,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>66360</t>
+          <t>71779</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>51948</t>
+          <t>56368</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>84937</t>
+          <t>92080</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>14,95%</t>
+          <t>14,84%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>11,7%</t>
+          <t>11,65%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>19,14%</t>
+          <t>19,03%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -11343,22 +11343,22 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>40906</t>
+          <t>44064</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>31110</t>
+          <t>34212</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>53144</t>
+          <t>57715</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>9,4%</t>
+          <t>9,21%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
@@ -11368,7 +11368,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>12,21%</t>
+          <t>12,07%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -11378,32 +11378,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>107266</t>
+          <t>115843</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>88990</t>
+          <t>96491</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>127580</t>
+          <t>137000</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>12,2%</t>
+          <t>12,04%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>10,12%</t>
+          <t>10,03%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>14,51%</t>
+          <t>14,24%</t>
         </is>
       </c>
     </row>
@@ -11421,32 +11421,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>323983</t>
+          <t>355181</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>302056</t>
+          <t>332251</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>342459</t>
+          <t>375070</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>72,99%</t>
+          <t>73,42%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>68,05%</t>
+          <t>68,68%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>77,16%</t>
+          <t>77,53%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -11456,32 +11456,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>366908</t>
+          <t>404027</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>353250</t>
+          <t>389727</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>379035</t>
+          <t>417214</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>84,3%</t>
+          <t>84,49%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>81,16%</t>
+          <t>81,5%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>87,09%</t>
+          <t>87,25%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -11491,32 +11491,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>690890</t>
+          <t>759209</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>666642</t>
+          <t>732426</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>712300</t>
+          <t>784082</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>78,59%</t>
+          <t>78,92%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>75,83%</t>
+          <t>76,14%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>81,03%</t>
+          <t>81,51%</t>
         </is>
       </c>
     </row>
@@ -11534,17 +11534,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>443855</t>
+          <t>483766</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>443855</t>
+          <t>483766</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>443855</t>
+          <t>483766</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -11569,17 +11569,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>435229</t>
+          <t>478200</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>435229</t>
+          <t>478200</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>435229</t>
+          <t>478200</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -11604,17 +11604,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>879083</t>
+          <t>961966</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>879083</t>
+          <t>961966</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>879083</t>
+          <t>961966</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -11651,32 +11651,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>40076</t>
+          <t>41391</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>25671</t>
+          <t>28807</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>56389</t>
+          <t>56089</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>2,05%</t>
+          <t>2,16%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>1,51%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>2,89%</t>
+          <t>2,93%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -11686,32 +11686,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>8763</t>
+          <t>10007</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>4546</t>
+          <t>5549</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>14930</t>
+          <t>16223</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,66%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>0,31%</t>
+          <t>0,37%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>1,07%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -11721,32 +11721,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>48839</t>
+          <t>51398</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>33451</t>
+          <t>39379</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>65265</t>
+          <t>67126</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>1,43%</t>
+          <t>1,5%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>1,15%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>1,91%</t>
+          <t>1,96%</t>
         </is>
       </c>
     </row>
@@ -11764,32 +11764,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>274027</t>
+          <t>30860</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>30007</t>
+          <t>20860</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>871801</t>
+          <t>44038</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>14,03%</t>
+          <t>1,61%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>1,54%</t>
+          <t>1,09%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>44,64%</t>
+          <t>2,3%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -11799,32 +11799,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>16093</t>
+          <t>18241</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>10652</t>
+          <t>12235</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>24327</t>
+          <t>26467</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>1,21%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,81%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>1,75%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -11834,32 +11834,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>290120</t>
+          <t>49101</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>43823</t>
+          <t>38350</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>944920</t>
+          <t>66737</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>8,5%</t>
+          <t>1,43%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>1,12%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>27,67%</t>
+          <t>1,95%</t>
         </is>
       </c>
     </row>
@@ -11877,32 +11877,32 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>58635</t>
+          <t>63255</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>36444</t>
+          <t>47431</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>80676</t>
+          <t>82986</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>3,0%</t>
+          <t>3,31%</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>1,87%</t>
+          <t>2,48%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>4,13%</t>
+          <t>4,34%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -11912,32 +11912,32 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>19932</t>
+          <t>21303</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>13291</t>
+          <t>14521</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>28540</t>
+          <t>30824</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>1,41%</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>0,96%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>1,95%</t>
+          <t>2,04%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -11947,32 +11947,32 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>78567</t>
+          <t>84558</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>58549</t>
+          <t>67098</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>101512</t>
+          <t>109300</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>2,47%</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>1,71%</t>
+          <t>1,96%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>2,97%</t>
+          <t>3,19%</t>
         </is>
       </c>
     </row>
@@ -11990,32 +11990,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>177222</t>
+          <t>196506</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>118333</t>
+          <t>168437</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>217210</t>
+          <t>225243</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>9,07%</t>
+          <t>10,28%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>6,06%</t>
+          <t>8,81%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>11,12%</t>
+          <t>11,78%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -12025,32 +12025,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>88575</t>
+          <t>98863</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>72461</t>
+          <t>82745</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>105677</t>
+          <t>116635</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>6,06%</t>
+          <t>6,54%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>4,96%</t>
+          <t>5,48%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>7,23%</t>
+          <t>7,72%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -12060,32 +12060,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>265797</t>
+          <t>295369</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>202738</t>
+          <t>263580</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>304356</t>
+          <t>330273</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>7,78%</t>
+          <t>8,63%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>5,94%</t>
+          <t>7,7%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>8,91%</t>
+          <t>9,65%</t>
         </is>
       </c>
     </row>
@@ -12103,32 +12103,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>1402915</t>
+          <t>1580083</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>905202</t>
+          <t>1540517</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>1616591</t>
+          <t>1614637</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>71,84%</t>
+          <t>82,64%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>46,35%</t>
+          <t>80,57%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>82,78%</t>
+          <t>84,44%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -12138,32 +12138,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>1328127</t>
+          <t>1362797</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>1307332</t>
+          <t>1343341</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>1350804</t>
+          <t>1382742</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>90,87%</t>
+          <t>90,18%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>89,45%</t>
+          <t>88,89%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>92,43%</t>
+          <t>91,5%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -12173,32 +12173,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>2731042</t>
+          <t>2942879</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>2155548</t>
+          <t>2896115</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>2956413</t>
+          <t>2982269</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>79,99%</t>
+          <t>85,97%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>63,13%</t>
+          <t>84,6%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>86,59%</t>
+          <t>87,12%</t>
         </is>
       </c>
     </row>
@@ -12216,17 +12216,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>1952875</t>
+          <t>1912096</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>1952875</t>
+          <t>1912096</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>1952875</t>
+          <t>1912096</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -12251,17 +12251,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>1461490</t>
+          <t>1511211</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>1461490</t>
+          <t>1511211</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>1461490</t>
+          <t>1511211</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -12286,17 +12286,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>3414365</t>
+          <t>3423306</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>3414365</t>
+          <t>3423306</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>3414365</t>
+          <t>3423306</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
